--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_electronics_consumer_office.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.102331777568172</v>
+        <v>0.1021096981242515</v>
       </c>
       <c r="C2">
-        <v>232.7740480104325</v>
+        <v>231.1327111230941</v>
       </c>
       <c r="D2">
-        <v>203.7740480104325</v>
+        <v>204.5777111230941</v>
       </c>
       <c r="E2">
-        <v>-53.7</v>
+        <v>-51.255</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.445</v>
       </c>
       <c r="G2">
         <v>29</v>
@@ -1582,28 +1582,28 @@
         <v>14.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1229835</v>
       </c>
       <c r="N2">
-        <v>14.6</v>
+        <v>14.4770165</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.619254125</v>
       </c>
       <c r="P2">
-        <v>10.95</v>
+        <v>10.857762375</v>
       </c>
       <c r="Q2">
-        <v>27.85</v>
+        <v>27.757762375</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.102331777568172</v>
+        <v>0.1027600486103551</v>
       </c>
       <c r="T2">
-        <v>1.101909567345926</v>
+        <v>1.110257367098546</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.7151121898466</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1021096981242515</v>
+        <v>0.1018876186803311</v>
       </c>
       <c r="C3">
-        <v>231.1327111230941</v>
+        <v>229.4977384587824</v>
       </c>
       <c r="D3">
-        <v>204.5777111230941</v>
+        <v>205.3877384587824</v>
       </c>
       <c r="E3">
-        <v>-51.255</v>
+        <v>-48.81</v>
       </c>
       <c r="F3">
-        <v>2.445</v>
+        <v>4.89</v>
       </c>
       <c r="G3">
         <v>29</v>
@@ -1664,28 +1664,28 @@
         <v>14.6</v>
       </c>
       <c r="M3">
-        <v>0.1229835</v>
+        <v>0.245967</v>
       </c>
       <c r="N3">
-        <v>14.4770165</v>
+        <v>14.354033</v>
       </c>
       <c r="O3">
-        <v>3.619254125</v>
+        <v>3.58850825</v>
       </c>
       <c r="P3">
-        <v>10.857762375</v>
+        <v>10.76552475</v>
       </c>
       <c r="Q3">
-        <v>27.757762375</v>
+        <v>27.66552475</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1027600486103551</v>
+        <v>0.1031970598778889</v>
       </c>
       <c r="T3">
-        <v>1.110257367098546</v>
+        <v>1.118775530111425</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.7151121898466</v>
+        <v>59.35755609492332</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1018876186803311</v>
+        <v>0.1016655392364107</v>
       </c>
       <c r="C4">
-        <v>229.4977384587824</v>
+        <v>227.8692059156162</v>
       </c>
       <c r="D4">
-        <v>205.3877384587824</v>
+        <v>206.2042059156163</v>
       </c>
       <c r="E4">
-        <v>-48.81</v>
+        <v>-46.365</v>
       </c>
       <c r="F4">
-        <v>4.89</v>
+        <v>7.335</v>
       </c>
       <c r="G4">
         <v>29</v>
@@ -1746,28 +1746,28 @@
         <v>14.6</v>
       </c>
       <c r="M4">
-        <v>0.245967</v>
+        <v>0.3689505</v>
       </c>
       <c r="N4">
-        <v>14.354033</v>
+        <v>14.2310495</v>
       </c>
       <c r="O4">
-        <v>3.58850825</v>
+        <v>3.557762375</v>
       </c>
       <c r="P4">
-        <v>10.76552475</v>
+        <v>10.673287125</v>
       </c>
       <c r="Q4">
-        <v>27.66552475</v>
+        <v>27.573287125</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1031970598778889</v>
+        <v>0.1036430816870213</v>
       </c>
       <c r="T4">
-        <v>1.118775530111425</v>
+        <v>1.127469325351373</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.35755609492332</v>
+        <v>39.57170406328221</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1016655392364107</v>
+        <v>0.1014434597924902</v>
       </c>
       <c r="C5">
-        <v>227.8692059156162</v>
+        <v>226.2471906033868</v>
       </c>
       <c r="D5">
-        <v>206.2042059156163</v>
+        <v>207.0271906033868</v>
       </c>
       <c r="E5">
-        <v>-46.365</v>
+        <v>-43.92</v>
       </c>
       <c r="F5">
-        <v>7.335</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G5">
         <v>29</v>
@@ -1828,28 +1828,28 @@
         <v>14.6</v>
       </c>
       <c r="M5">
-        <v>0.3689505</v>
+        <v>0.4919339999999999</v>
       </c>
       <c r="N5">
-        <v>14.2310495</v>
+        <v>14.108066</v>
       </c>
       <c r="O5">
-        <v>3.557762375</v>
+        <v>3.5270165</v>
       </c>
       <c r="P5">
-        <v>10.673287125</v>
+        <v>10.5810495</v>
       </c>
       <c r="Q5">
-        <v>27.573287125</v>
+        <v>27.4810495</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1036430816870213</v>
+        <v>0.1040983956171773</v>
       </c>
       <c r="T5">
-        <v>1.127469325351373</v>
+        <v>1.136344241325486</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.57170406328221</v>
+        <v>29.67877804746166</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1014434597924902</v>
+        <v>0.1012213803485698</v>
       </c>
       <c r="C6">
-        <v>226.2471906033868</v>
+        <v>224.6317708678342</v>
       </c>
       <c r="D6">
-        <v>207.0271906033868</v>
+        <v>207.8567708678342</v>
       </c>
       <c r="E6">
-        <v>-43.92</v>
+        <v>-41.475</v>
       </c>
       <c r="F6">
-        <v>9.779999999999999</v>
+        <v>12.225</v>
       </c>
       <c r="G6">
         <v>29</v>
@@ -1910,28 +1910,28 @@
         <v>14.6</v>
       </c>
       <c r="M6">
-        <v>0.4919339999999999</v>
+        <v>0.6149175</v>
       </c>
       <c r="N6">
-        <v>14.108066</v>
+        <v>13.9850825</v>
       </c>
       <c r="O6">
-        <v>3.5270165</v>
+        <v>3.496270625</v>
       </c>
       <c r="P6">
-        <v>10.5810495</v>
+        <v>10.488811875</v>
       </c>
       <c r="Q6">
-        <v>27.4810495</v>
+        <v>27.388811875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1040983956171773</v>
+        <v>0.1045632951037577</v>
       </c>
       <c r="T6">
-        <v>1.136344241325486</v>
+        <v>1.145405997635897</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.67877804746166</v>
+        <v>23.74302243796932</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1012213803485698</v>
+        <v>0.1009993009046494</v>
       </c>
       <c r="C7">
-        <v>224.6317708678342</v>
+        <v>223.0230263155104</v>
       </c>
       <c r="D7">
-        <v>207.8567708678342</v>
+        <v>208.6930263155104</v>
       </c>
       <c r="E7">
-        <v>-41.475</v>
+        <v>-39.03</v>
       </c>
       <c r="F7">
-        <v>12.225</v>
+        <v>14.67</v>
       </c>
       <c r="G7">
         <v>29</v>
@@ -1992,28 +1992,28 @@
         <v>14.6</v>
       </c>
       <c r="M7">
-        <v>0.6149175</v>
+        <v>0.737901</v>
       </c>
       <c r="N7">
-        <v>13.9850825</v>
+        <v>13.862099</v>
       </c>
       <c r="O7">
-        <v>3.496270625</v>
+        <v>3.46552475</v>
       </c>
       <c r="P7">
-        <v>10.488811875</v>
+        <v>10.39657425</v>
       </c>
       <c r="Q7">
-        <v>27.388811875</v>
+        <v>27.29657425</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1045632951037577</v>
+        <v>0.1050380860687759</v>
       </c>
       <c r="T7">
-        <v>1.145405997635897</v>
+        <v>1.154660557272061</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.74302243796932</v>
+        <v>19.7858520316411</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1009993009046494</v>
+        <v>0.100777221460729</v>
       </c>
       <c r="C8">
-        <v>223.0230263155104</v>
+        <v>221.4210378392433</v>
       </c>
       <c r="D8">
-        <v>208.6930263155104</v>
+        <v>209.5360378392433</v>
       </c>
       <c r="E8">
-        <v>-39.03</v>
+        <v>-36.58500000000001</v>
       </c>
       <c r="F8">
-        <v>14.67</v>
+        <v>17.115</v>
       </c>
       <c r="G8">
         <v>29</v>
@@ -2074,28 +2074,28 @@
         <v>14.6</v>
       </c>
       <c r="M8">
-        <v>0.7379009999999999</v>
+        <v>0.8608844999999998</v>
       </c>
       <c r="N8">
-        <v>13.862099</v>
+        <v>13.7391155</v>
       </c>
       <c r="O8">
-        <v>3.46552475</v>
+        <v>3.434778875000001</v>
       </c>
       <c r="P8">
-        <v>10.39657425</v>
+        <v>10.304336625</v>
       </c>
       <c r="Q8">
-        <v>27.29657425</v>
+        <v>27.204336625</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1050380860687759</v>
+        <v>0.1055230875921817</v>
       </c>
       <c r="T8">
-        <v>1.154660557272061</v>
+        <v>1.164114139696099</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.7858520316411</v>
+        <v>16.95930174140666</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.100777221460729</v>
+        <v>0.1005551420168085</v>
       </c>
       <c r="C9">
-        <v>221.4210378392434</v>
+        <v>219.8258876442232</v>
       </c>
       <c r="D9">
-        <v>209.5360378392434</v>
+        <v>210.3858876442232</v>
       </c>
       <c r="E9">
-        <v>-36.585</v>
+        <v>-34.14</v>
       </c>
       <c r="F9">
-        <v>17.115</v>
+        <v>19.56</v>
       </c>
       <c r="G9">
         <v>29</v>
@@ -2156,28 +2156,28 @@
         <v>14.6</v>
       </c>
       <c r="M9">
-        <v>0.8608845000000001</v>
+        <v>0.9838679999999999</v>
       </c>
       <c r="N9">
-        <v>13.7391155</v>
+        <v>13.616132</v>
       </c>
       <c r="O9">
-        <v>3.434778875</v>
+        <v>3.404033000000001</v>
       </c>
       <c r="P9">
-        <v>10.304336625</v>
+        <v>10.212099</v>
       </c>
       <c r="Q9">
-        <v>27.204336625</v>
+        <v>27.112099</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1055230875921817</v>
+        <v>0.1060186326269658</v>
       </c>
       <c r="T9">
-        <v>1.164114139696099</v>
+        <v>1.17377323478153</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.95930174140666</v>
+        <v>14.83938902373083</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1005551420168085</v>
+        <v>0.1003330625728881</v>
       </c>
       <c r="C10">
-        <v>219.8258876442232</v>
+        <v>218.2376592747233</v>
       </c>
       <c r="D10">
-        <v>210.3858876442232</v>
+        <v>211.2426592747233</v>
       </c>
       <c r="E10">
-        <v>-34.14</v>
+        <v>-31.695</v>
       </c>
       <c r="F10">
-        <v>19.56</v>
+        <v>22.005</v>
       </c>
       <c r="G10">
         <v>29</v>
@@ -2238,28 +2238,28 @@
         <v>14.6</v>
       </c>
       <c r="M10">
-        <v>0.9838679999999999</v>
+        <v>1.1068515</v>
       </c>
       <c r="N10">
-        <v>13.616132</v>
+        <v>13.4931485</v>
       </c>
       <c r="O10">
-        <v>3.404033000000001</v>
+        <v>3.373287125</v>
       </c>
       <c r="P10">
-        <v>10.212099</v>
+        <v>10.119861375</v>
       </c>
       <c r="Q10">
-        <v>27.112099</v>
+        <v>27.019861375</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1060186326269658</v>
+        <v>0.1065250687614155</v>
       </c>
       <c r="T10">
-        <v>1.17377323478153</v>
+        <v>1.183644617671036</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.83938902373083</v>
+        <v>13.19056802109407</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1003330625728881</v>
+        <v>0.1002234831289677</v>
       </c>
       <c r="C11">
-        <v>218.2376592747233</v>
+        <v>216.2179876771841</v>
       </c>
       <c r="D11">
-        <v>211.2426592747233</v>
+        <v>211.6679876771841</v>
       </c>
       <c r="E11">
-        <v>-31.695</v>
+        <v>-29.25</v>
       </c>
       <c r="F11">
-        <v>22.005</v>
+        <v>24.45</v>
       </c>
       <c r="G11">
         <v>29</v>
@@ -2320,45 +2320,45 @@
         <v>14.6</v>
       </c>
       <c r="M11">
-        <v>1.1068515</v>
+        <v>1.26651</v>
       </c>
       <c r="N11">
-        <v>13.4931485</v>
+        <v>13.33349</v>
       </c>
       <c r="O11">
-        <v>3.373287125</v>
+        <v>3.3333725</v>
       </c>
       <c r="P11">
-        <v>10.119861375</v>
+        <v>10.0001175</v>
       </c>
       <c r="Q11">
-        <v>27.019861375</v>
+        <v>26.9001175</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1065250687614155</v>
+        <v>0.1070427590321863</v>
       </c>
       <c r="T11">
-        <v>1.183644617671036</v>
+        <v>1.193735364624753</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.19056802109407</v>
+        <v>11.52774158909128</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1002234831289677</v>
+        <v>0.1000126536850472</v>
       </c>
       <c r="C12">
-        <v>216.2179876771841</v>
+        <v>214.5961505571455</v>
       </c>
       <c r="D12">
-        <v>211.6679876771841</v>
+        <v>212.4911505571455</v>
       </c>
       <c r="E12">
-        <v>-29.25</v>
+        <v>-26.805</v>
       </c>
       <c r="F12">
-        <v>24.45</v>
+        <v>26.895</v>
       </c>
       <c r="G12">
         <v>29</v>
@@ -2402,28 +2402,28 @@
         <v>14.6</v>
       </c>
       <c r="M12">
-        <v>1.26651</v>
+        <v>1.393161</v>
       </c>
       <c r="N12">
-        <v>13.33349</v>
+        <v>13.206839</v>
       </c>
       <c r="O12">
-        <v>3.3333725</v>
+        <v>3.301709750000001</v>
       </c>
       <c r="P12">
-        <v>10.0001175</v>
+        <v>9.905129250000002</v>
       </c>
       <c r="Q12">
-        <v>26.9001175</v>
+        <v>26.80512925</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1070427590321863</v>
+        <v>0.1075720827921879</v>
       </c>
       <c r="T12">
-        <v>1.193735364624753</v>
+        <v>1.204052869936981</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.52774158909128</v>
+        <v>10.47976508099208</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1000126536850472</v>
+        <v>0.0999548242411268</v>
       </c>
       <c r="C13">
-        <v>214.5961505571455</v>
+        <v>212.3780600753082</v>
       </c>
       <c r="D13">
-        <v>212.4911505571455</v>
+        <v>212.7180600753082</v>
       </c>
       <c r="E13">
-        <v>-26.805</v>
+        <v>-24.36</v>
       </c>
       <c r="F13">
-        <v>26.895</v>
+        <v>29.34</v>
       </c>
       <c r="G13">
         <v>29</v>
@@ -2484,45 +2484,45 @@
         <v>14.6</v>
       </c>
       <c r="M13">
-        <v>1.393161</v>
+        <v>1.56969</v>
       </c>
       <c r="N13">
-        <v>13.206839</v>
+        <v>13.03031</v>
       </c>
       <c r="O13">
-        <v>3.301709750000001</v>
+        <v>3.2575775</v>
       </c>
       <c r="P13">
-        <v>9.905129250000002</v>
+        <v>9.772732500000002</v>
       </c>
       <c r="Q13">
-        <v>26.80512925</v>
+        <v>26.6727325</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1075720827921879</v>
+        <v>0.1081134366376441</v>
       </c>
       <c r="T13">
-        <v>1.204052869936981</v>
+        <v>1.214604864006305</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.47976508099208</v>
+        <v>9.301199599921004</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0999548242411268</v>
+        <v>0.09975674479720638</v>
       </c>
       <c r="C14">
-        <v>212.3780600753082</v>
+        <v>210.7139647649797</v>
       </c>
       <c r="D14">
-        <v>212.7180600753082</v>
+        <v>213.4989647649797</v>
       </c>
       <c r="E14">
-        <v>-24.36</v>
+        <v>-21.915</v>
       </c>
       <c r="F14">
-        <v>29.34</v>
+        <v>31.785</v>
       </c>
       <c r="G14">
         <v>29</v>
@@ -2566,28 +2566,28 @@
         <v>14.6</v>
       </c>
       <c r="M14">
-        <v>1.56969</v>
+        <v>1.7004975</v>
       </c>
       <c r="N14">
-        <v>13.03031</v>
+        <v>12.8995025</v>
       </c>
       <c r="O14">
-        <v>3.2575775</v>
+        <v>3.224875625</v>
       </c>
       <c r="P14">
-        <v>9.772732500000002</v>
+        <v>9.674626875000001</v>
       </c>
       <c r="Q14">
-        <v>26.6727325</v>
+        <v>26.574626875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1081134366376441</v>
+        <v>0.1086672353990878</v>
       </c>
       <c r="T14">
-        <v>1.214604864006305</v>
+        <v>1.225399432651935</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.301199599921004</v>
+        <v>8.585722707619389</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09975674479720638</v>
+        <v>0.09955866535328593</v>
       </c>
       <c r="C15">
-        <v>210.7139647649797</v>
+        <v>209.0556241052055</v>
       </c>
       <c r="D15">
-        <v>213.4989647649797</v>
+        <v>214.2856241052056</v>
       </c>
       <c r="E15">
-        <v>-21.915</v>
+        <v>-19.47</v>
       </c>
       <c r="F15">
-        <v>31.785</v>
+        <v>34.23</v>
       </c>
       <c r="G15">
         <v>29</v>
@@ -2648,28 +2648,28 @@
         <v>14.6</v>
       </c>
       <c r="M15">
-        <v>1.7004975</v>
+        <v>1.831305</v>
       </c>
       <c r="N15">
-        <v>12.8995025</v>
+        <v>12.768695</v>
       </c>
       <c r="O15">
-        <v>3.224875625</v>
+        <v>3.19217375</v>
       </c>
       <c r="P15">
-        <v>9.674626875000001</v>
+        <v>9.576521250000001</v>
       </c>
       <c r="Q15">
-        <v>26.574626875</v>
+        <v>26.47652125</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1086672353990878</v>
+        <v>0.1092339132014953</v>
       </c>
       <c r="T15">
-        <v>1.225399432651935</v>
+        <v>1.236445037777696</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.585722707619389</v>
+        <v>7.972456799932289</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09955866535328593</v>
+        <v>0.09945058590936551</v>
       </c>
       <c r="C16">
-        <v>209.0556241052055</v>
+        <v>207.0423038473906</v>
       </c>
       <c r="D16">
-        <v>214.2856241052056</v>
+        <v>214.7173038473906</v>
       </c>
       <c r="E16">
-        <v>-19.47</v>
+        <v>-17.025</v>
       </c>
       <c r="F16">
-        <v>34.23</v>
+        <v>36.675</v>
       </c>
       <c r="G16">
         <v>29</v>
@@ -2730,45 +2730,45 @@
         <v>14.6</v>
       </c>
       <c r="M16">
-        <v>1.831305</v>
+        <v>1.9914525</v>
       </c>
       <c r="N16">
-        <v>12.768695</v>
+        <v>12.6085475</v>
       </c>
       <c r="O16">
-        <v>3.19217375</v>
+        <v>3.152136875</v>
       </c>
       <c r="P16">
-        <v>9.576521250000001</v>
+        <v>9.456410625</v>
       </c>
       <c r="Q16">
-        <v>26.47652125</v>
+        <v>26.356410625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1092339132014953</v>
+        <v>0.1098139245992535</v>
       </c>
       <c r="T16">
-        <v>1.236445037777696</v>
+        <v>1.247750539494651</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.972456799932289</v>
+        <v>7.331332281337365</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09945058590936551</v>
+        <v>0.09925850646544508</v>
       </c>
       <c r="C17">
-        <v>207.0423038473906</v>
+        <v>205.3687952909414</v>
       </c>
       <c r="D17">
-        <v>214.7173038473906</v>
+        <v>215.4887952909415</v>
       </c>
       <c r="E17">
-        <v>-17.02500000000001</v>
+        <v>-14.58000000000001</v>
       </c>
       <c r="F17">
-        <v>36.675</v>
+        <v>39.12</v>
       </c>
       <c r="G17">
         <v>29</v>
@@ -2812,28 +2812,28 @@
         <v>14.6</v>
       </c>
       <c r="M17">
-        <v>1.9914525</v>
+        <v>2.124216</v>
       </c>
       <c r="N17">
-        <v>12.6085475</v>
+        <v>12.475784</v>
       </c>
       <c r="O17">
-        <v>3.152136875000001</v>
+        <v>3.118946</v>
       </c>
       <c r="P17">
-        <v>9.456410625000002</v>
+        <v>9.356838</v>
       </c>
       <c r="Q17">
-        <v>26.356410625</v>
+        <v>26.256838</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1098139245992535</v>
+        <v>0.1104077457921965</v>
       </c>
       <c r="T17">
-        <v>1.247750539494651</v>
+        <v>1.259325219823915</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.331332281337367</v>
+        <v>6.87312401375378</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09925850646544508</v>
+        <v>0.09906642702152467</v>
       </c>
       <c r="C18">
-        <v>205.3687952909414</v>
+        <v>203.7008507512944</v>
       </c>
       <c r="D18">
-        <v>215.4887952909415</v>
+        <v>216.2658507512944</v>
       </c>
       <c r="E18">
-        <v>-14.58000000000001</v>
+        <v>-12.135</v>
       </c>
       <c r="F18">
-        <v>39.12</v>
+        <v>41.565</v>
       </c>
       <c r="G18">
         <v>29</v>
@@ -2894,28 +2894,28 @@
         <v>14.6</v>
       </c>
       <c r="M18">
-        <v>2.124216</v>
+        <v>2.2569795</v>
       </c>
       <c r="N18">
-        <v>12.475784</v>
+        <v>12.3430205</v>
       </c>
       <c r="O18">
-        <v>3.118946</v>
+        <v>3.085755125</v>
       </c>
       <c r="P18">
-        <v>9.356838</v>
+        <v>9.257265375000001</v>
       </c>
       <c r="Q18">
-        <v>26.256838</v>
+        <v>26.157265375</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1104077457921965</v>
+        <v>0.1110158759295478</v>
       </c>
       <c r="T18">
-        <v>1.259325219823915</v>
+        <v>1.27117880811292</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.87312401375378</v>
+        <v>6.468822601180028</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09906642702152467</v>
+        <v>0.09900934757760423</v>
       </c>
       <c r="C19">
-        <v>203.7008507512944</v>
+        <v>201.4878463509747</v>
       </c>
       <c r="D19">
-        <v>216.2658507512944</v>
+        <v>216.4978463509747</v>
       </c>
       <c r="E19">
-        <v>-12.135</v>
+        <v>-9.689999999999998</v>
       </c>
       <c r="F19">
-        <v>41.565</v>
+        <v>44.01000000000001</v>
       </c>
       <c r="G19">
         <v>29</v>
@@ -2976,45 +2976,45 @@
         <v>14.6</v>
       </c>
       <c r="M19">
-        <v>2.2569795</v>
+        <v>2.433753</v>
       </c>
       <c r="N19">
-        <v>12.3430205</v>
+        <v>12.166247</v>
       </c>
       <c r="O19">
-        <v>3.085755125</v>
+        <v>3.041561750000001</v>
       </c>
       <c r="P19">
-        <v>9.257265375000001</v>
+        <v>9.124685250000002</v>
       </c>
       <c r="Q19">
-        <v>26.157265375</v>
+        <v>26.02468525</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1110158759295478</v>
+        <v>0.1116388385092734</v>
       </c>
       <c r="T19">
-        <v>1.27117880811292</v>
+        <v>1.283321508311414</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.468822601180028</v>
+        <v>5.998965383915295</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09900934757760424</v>
+        <v>0.09882476813368382</v>
       </c>
       <c r="C20">
-        <v>201.4878463509746</v>
+        <v>199.7964762770628</v>
       </c>
       <c r="D20">
-        <v>216.4978463509746</v>
+        <v>217.2514762770628</v>
       </c>
       <c r="E20">
-        <v>-9.690000000000005</v>
+        <v>-7.245000000000005</v>
       </c>
       <c r="F20">
-        <v>44.01</v>
+        <v>46.455</v>
       </c>
       <c r="G20">
         <v>29</v>
@@ -3058,28 +3058,28 @@
         <v>14.6</v>
       </c>
       <c r="M20">
-        <v>2.433753</v>
+        <v>2.5689615</v>
       </c>
       <c r="N20">
-        <v>12.166247</v>
+        <v>12.0310385</v>
       </c>
       <c r="O20">
-        <v>3.041561750000001</v>
+        <v>3.007759625</v>
       </c>
       <c r="P20">
-        <v>9.124685250000002</v>
+        <v>9.023278875000001</v>
       </c>
       <c r="Q20">
-        <v>26.02468525</v>
+        <v>25.923278875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1116388385092734</v>
+        <v>0.1122771828810911</v>
       </c>
       <c r="T20">
-        <v>1.283321508311414</v>
+        <v>1.295764028267894</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.998965383915296</v>
+        <v>5.683230363709227</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09882476813368382</v>
+        <v>0.09864018868976336</v>
       </c>
       <c r="C21">
-        <v>199.7964762770628</v>
+        <v>198.1103713089779</v>
       </c>
       <c r="D21">
-        <v>217.2514762770628</v>
+        <v>218.0103713089779</v>
       </c>
       <c r="E21">
-        <v>-7.245000000000005</v>
+        <v>-4.799999999999997</v>
       </c>
       <c r="F21">
-        <v>46.455</v>
+        <v>48.90000000000001</v>
       </c>
       <c r="G21">
         <v>29</v>
@@ -3140,28 +3140,28 @@
         <v>14.6</v>
       </c>
       <c r="M21">
-        <v>2.5689615</v>
+        <v>2.70417</v>
       </c>
       <c r="N21">
-        <v>12.0310385</v>
+        <v>11.89583</v>
       </c>
       <c r="O21">
-        <v>3.007759625</v>
+        <v>2.9739575</v>
       </c>
       <c r="P21">
-        <v>9.023278875000001</v>
+        <v>8.921872499999999</v>
       </c>
       <c r="Q21">
-        <v>25.923278875</v>
+        <v>25.8218725</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1122771828810911</v>
+        <v>0.1129314858622042</v>
       </c>
       <c r="T21">
-        <v>1.295764028267894</v>
+        <v>1.308517611223287</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.683230363709227</v>
+        <v>5.399068845523765</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09864018868976336</v>
+        <v>0.09845560924584293</v>
       </c>
       <c r="C22">
-        <v>198.1103713089779</v>
+        <v>196.429586815767</v>
       </c>
       <c r="D22">
-        <v>218.0103713089779</v>
+        <v>218.774586815767</v>
       </c>
       <c r="E22">
-        <v>-4.799999999999997</v>
+        <v>-2.354999999999997</v>
       </c>
       <c r="F22">
-        <v>48.90000000000001</v>
+        <v>51.34500000000001</v>
       </c>
       <c r="G22">
         <v>29</v>
@@ -3222,28 +3222,28 @@
         <v>14.6</v>
       </c>
       <c r="M22">
-        <v>2.70417</v>
+        <v>2.8393785</v>
       </c>
       <c r="N22">
-        <v>11.89583</v>
+        <v>11.7606215</v>
       </c>
       <c r="O22">
-        <v>2.9739575</v>
+        <v>2.940155375</v>
       </c>
       <c r="P22">
-        <v>8.921872499999999</v>
+        <v>8.820466125000001</v>
       </c>
       <c r="Q22">
-        <v>25.8218725</v>
+        <v>25.720466125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1129314858622042</v>
+        <v>0.1136023534757505</v>
       </c>
       <c r="T22">
-        <v>1.308517611223287</v>
+        <v>1.321594069696538</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.399068845523765</v>
+        <v>5.141970329070253</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09845560924584293</v>
+        <v>0.09827102980192251</v>
       </c>
       <c r="C23">
-        <v>196.429586815767</v>
+        <v>194.7541789455729</v>
       </c>
       <c r="D23">
-        <v>218.774586815767</v>
+        <v>219.5441789455729</v>
       </c>
       <c r="E23">
-        <v>-2.355000000000004</v>
+        <v>0.08999999999999631</v>
       </c>
       <c r="F23">
-        <v>51.345</v>
+        <v>53.79</v>
       </c>
       <c r="G23">
         <v>29</v>
@@ -3304,28 +3304,28 @@
         <v>14.6</v>
       </c>
       <c r="M23">
-        <v>2.8393785</v>
+        <v>2.974587</v>
       </c>
       <c r="N23">
-        <v>11.7606215</v>
+        <v>11.625413</v>
       </c>
       <c r="O23">
-        <v>2.940155375</v>
+        <v>2.90635325</v>
       </c>
       <c r="P23">
-        <v>8.820466125000001</v>
+        <v>8.719059750000001</v>
       </c>
       <c r="Q23">
-        <v>25.720466125</v>
+        <v>25.61905975</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1136023534757505</v>
+        <v>0.1142904228229776</v>
       </c>
       <c r="T23">
-        <v>1.321594069696538</v>
+        <v>1.335005821976795</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.141970329070253</v>
+        <v>4.908244405021605</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09827102980192251</v>
+        <v>0.09808645035800208</v>
       </c>
       <c r="C24">
-        <v>194.7541789455729</v>
+        <v>193.0842046393862</v>
       </c>
       <c r="D24">
-        <v>219.5441789455729</v>
+        <v>220.3192046393862</v>
       </c>
       <c r="E24">
-        <v>0.08999999999999631</v>
+        <v>2.534999999999997</v>
       </c>
       <c r="F24">
-        <v>53.79</v>
+        <v>56.235</v>
       </c>
       <c r="G24">
         <v>29</v>
@@ -3386,28 +3386,28 @@
         <v>14.6</v>
       </c>
       <c r="M24">
-        <v>2.974587</v>
+        <v>3.1097955</v>
       </c>
       <c r="N24">
-        <v>11.625413</v>
+        <v>11.4902045</v>
       </c>
       <c r="O24">
-        <v>2.90635325</v>
+        <v>2.872551125</v>
       </c>
       <c r="P24">
-        <v>8.719059750000001</v>
+        <v>8.617653375</v>
       </c>
       <c r="Q24">
-        <v>25.61905975</v>
+        <v>25.517653375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1142904228229776</v>
+        <v>0.1149963641013014</v>
       </c>
       <c r="T24">
-        <v>1.335005821976795</v>
+        <v>1.348765931459136</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.908244405021605</v>
+        <v>4.694842474368492</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09808645035800208</v>
+        <v>0.09835187091408165</v>
       </c>
       <c r="C25">
-        <v>193.0842046393862</v>
+        <v>189.5264517574574</v>
       </c>
       <c r="D25">
-        <v>220.3192046393862</v>
+        <v>219.2064517574574</v>
       </c>
       <c r="E25">
-        <v>2.534999999999997</v>
+        <v>4.980000000000004</v>
       </c>
       <c r="F25">
-        <v>56.235</v>
+        <v>58.68000000000001</v>
       </c>
       <c r="G25">
         <v>29</v>
@@ -3468,45 +3468,45 @@
         <v>14.6</v>
       </c>
       <c r="M25">
-        <v>3.1097955</v>
+        <v>3.391704000000001</v>
       </c>
       <c r="N25">
-        <v>11.4902045</v>
+        <v>11.208296</v>
       </c>
       <c r="O25">
-        <v>2.872551125</v>
+        <v>2.802074</v>
       </c>
       <c r="P25">
-        <v>8.617653375</v>
+        <v>8.406222</v>
       </c>
       <c r="Q25">
-        <v>25.517653375</v>
+        <v>25.306222</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1149963641013014</v>
+        <v>0.1157208827816864</v>
       </c>
       <c r="T25">
-        <v>1.348765931459136</v>
+        <v>1.362888149085751</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.694842474368492</v>
+        <v>4.304620922108768</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09835187091408165</v>
+        <v>0.09818604147016122</v>
       </c>
       <c r="C26">
-        <v>189.5264517574574</v>
+        <v>187.7753557627717</v>
       </c>
       <c r="D26">
-        <v>219.2064517574574</v>
+        <v>219.9003557627717</v>
       </c>
       <c r="E26">
-        <v>4.979999999999997</v>
+        <v>7.424999999999997</v>
       </c>
       <c r="F26">
-        <v>58.68</v>
+        <v>61.125</v>
       </c>
       <c r="G26">
         <v>29</v>
@@ -3550,28 +3550,28 @@
         <v>14.6</v>
       </c>
       <c r="M26">
-        <v>3.391704</v>
+        <v>3.533025</v>
       </c>
       <c r="N26">
-        <v>11.208296</v>
+        <v>11.066975</v>
       </c>
       <c r="O26">
-        <v>2.802074</v>
+        <v>2.76674375</v>
       </c>
       <c r="P26">
-        <v>8.406222</v>
+        <v>8.300231250000001</v>
       </c>
       <c r="Q26">
-        <v>25.306222</v>
+        <v>25.20023125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1157208827816864</v>
+        <v>0.116464721960215</v>
       </c>
       <c r="T26">
-        <v>1.362888149085751</v>
+        <v>1.377386959182407</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.304620922108769</v>
+        <v>4.132436085224418</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09818604147016122</v>
+        <v>0.09870271202624079</v>
       </c>
       <c r="C27">
-        <v>187.7753557627717</v>
+        <v>183.1827146543596</v>
       </c>
       <c r="D27">
-        <v>219.9003557627717</v>
+        <v>217.7527146543596</v>
       </c>
       <c r="E27">
-        <v>7.424999999999997</v>
+        <v>9.869999999999997</v>
       </c>
       <c r="F27">
-        <v>61.125</v>
+        <v>63.57</v>
       </c>
       <c r="G27">
         <v>29</v>
@@ -3632,45 +3632,45 @@
         <v>14.6</v>
       </c>
       <c r="M27">
-        <v>3.533025</v>
+        <v>3.896841</v>
       </c>
       <c r="N27">
-        <v>11.066975</v>
+        <v>10.703159</v>
       </c>
       <c r="O27">
-        <v>2.76674375</v>
+        <v>2.67578975</v>
       </c>
       <c r="P27">
-        <v>8.300231250000001</v>
+        <v>8.027369250000001</v>
       </c>
       <c r="Q27">
-        <v>25.20023125</v>
+        <v>24.92736925</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.116464721960215</v>
+        <v>0.1172286649003254</v>
       </c>
       <c r="T27">
-        <v>1.377386959182407</v>
+        <v>1.392277629011406</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.132436085224418</v>
+        <v>3.746624509442392</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09870271202624079</v>
+        <v>0.09856313258232037</v>
       </c>
       <c r="C28">
-        <v>183.1827146543596</v>
+        <v>181.3137570789862</v>
       </c>
       <c r="D28">
-        <v>217.7527146543596</v>
+        <v>218.3287570789862</v>
       </c>
       <c r="E28">
-        <v>9.869999999999997</v>
+        <v>12.315</v>
       </c>
       <c r="F28">
-        <v>63.57</v>
+        <v>66.015</v>
       </c>
       <c r="G28">
         <v>29</v>
@@ -3714,28 +3714,28 @@
         <v>14.6</v>
       </c>
       <c r="M28">
-        <v>3.896841</v>
+        <v>4.0467195</v>
       </c>
       <c r="N28">
-        <v>10.703159</v>
+        <v>10.5532805</v>
       </c>
       <c r="O28">
-        <v>2.67578975</v>
+        <v>2.638320125</v>
       </c>
       <c r="P28">
-        <v>8.027369250000001</v>
+        <v>7.914960375000001</v>
       </c>
       <c r="Q28">
-        <v>24.92736925</v>
+        <v>24.814960375</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1172286649003254</v>
+        <v>0.1180135377840005</v>
       </c>
       <c r="T28">
-        <v>1.392277629011406</v>
+        <v>1.407576262397364</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.746624509442392</v>
+        <v>3.607860638722304</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09856313258232037</v>
+        <v>0.09901155313839992</v>
       </c>
       <c r="C29">
-        <v>181.3137570789862</v>
+        <v>177.0288727515569</v>
       </c>
       <c r="D29">
-        <v>218.3287570789862</v>
+        <v>216.4888727515569</v>
       </c>
       <c r="E29">
-        <v>12.315</v>
+        <v>14.76000000000001</v>
       </c>
       <c r="F29">
-        <v>66.015</v>
+        <v>68.46000000000001</v>
       </c>
       <c r="G29">
         <v>29</v>
@@ -3796,45 +3796,45 @@
         <v>14.6</v>
       </c>
       <c r="M29">
-        <v>4.0467195</v>
+        <v>4.388286000000001</v>
       </c>
       <c r="N29">
-        <v>10.5532805</v>
+        <v>10.211714</v>
       </c>
       <c r="O29">
-        <v>2.638320125</v>
+        <v>2.5529285</v>
       </c>
       <c r="P29">
-        <v>7.914960375000001</v>
+        <v>7.6587855</v>
       </c>
       <c r="Q29">
-        <v>24.814960375</v>
+        <v>24.5587855</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1180135377840005</v>
+        <v>0.1188202126922221</v>
       </c>
       <c r="T29">
-        <v>1.407576262397364</v>
+        <v>1.423299857821821</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.607860638722304</v>
+        <v>3.327039304183911</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09901155313839992</v>
+        <v>0.09889297369447948</v>
       </c>
       <c r="C30">
-        <v>177.0288727515569</v>
+        <v>175.0673855096398</v>
       </c>
       <c r="D30">
-        <v>216.4888727515569</v>
+        <v>216.9723855096398</v>
       </c>
       <c r="E30">
-        <v>14.76000000000001</v>
+        <v>17.20500000000001</v>
       </c>
       <c r="F30">
-        <v>68.46000000000001</v>
+        <v>70.90500000000002</v>
       </c>
       <c r="G30">
         <v>29</v>
@@ -3878,28 +3878,28 @@
         <v>14.6</v>
       </c>
       <c r="M30">
-        <v>4.388286000000001</v>
+        <v>4.545010500000001</v>
       </c>
       <c r="N30">
-        <v>10.211714</v>
+        <v>10.0549895</v>
       </c>
       <c r="O30">
-        <v>2.5529285</v>
+        <v>2.513747375</v>
       </c>
       <c r="P30">
-        <v>7.6587855</v>
+        <v>7.541242125000001</v>
       </c>
       <c r="Q30">
-        <v>24.5587855</v>
+        <v>24.441242125</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1188202126922221</v>
+        <v>0.1196496108372951</v>
       </c>
       <c r="T30">
-        <v>1.423299857821821</v>
+        <v>1.439466371427248</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.327039304183911</v>
+        <v>3.21231381093619</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09889297369447948</v>
+        <v>0.09877439425055906</v>
       </c>
       <c r="C31">
-        <v>175.0673855096398</v>
+        <v>173.1080628861121</v>
       </c>
       <c r="D31">
-        <v>216.9723855096398</v>
+        <v>217.4580628861121</v>
       </c>
       <c r="E31">
-        <v>17.205</v>
+        <v>19.64999999999999</v>
       </c>
       <c r="F31">
-        <v>70.905</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="G31">
         <v>29</v>
@@ -3960,28 +3960,28 @@
         <v>14.6</v>
       </c>
       <c r="M31">
-        <v>4.5450105</v>
+        <v>4.701735</v>
       </c>
       <c r="N31">
-        <v>10.0549895</v>
+        <v>9.898265000000002</v>
       </c>
       <c r="O31">
-        <v>2.513747375</v>
+        <v>2.474566250000001</v>
       </c>
       <c r="P31">
-        <v>7.541242125000001</v>
+        <v>7.423698750000002</v>
       </c>
       <c r="Q31">
-        <v>24.441242125</v>
+        <v>24.32369875</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1196496108372951</v>
+        <v>0.1205027060722272</v>
       </c>
       <c r="T31">
-        <v>1.439466371427248</v>
+        <v>1.456094785421402</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.212313810936191</v>
+        <v>3.105236683904984</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09877439425055906</v>
+        <v>0.09865581480663864</v>
       </c>
       <c r="C32">
-        <v>173.1080628861121</v>
+        <v>171.1509194496213</v>
       </c>
       <c r="D32">
-        <v>217.4580628861121</v>
+        <v>217.9459194496213</v>
       </c>
       <c r="E32">
-        <v>19.64999999999999</v>
+        <v>22.095</v>
       </c>
       <c r="F32">
-        <v>73.34999999999999</v>
+        <v>75.795</v>
       </c>
       <c r="G32">
         <v>29</v>
@@ -4042,28 +4042,28 @@
         <v>14.6</v>
       </c>
       <c r="M32">
-        <v>4.701735</v>
+        <v>4.8584595</v>
       </c>
       <c r="N32">
-        <v>9.898265000000002</v>
+        <v>9.741540500000001</v>
       </c>
       <c r="O32">
-        <v>2.474566250000001</v>
+        <v>2.435385125</v>
       </c>
       <c r="P32">
-        <v>7.423698750000002</v>
+        <v>7.306155375000001</v>
       </c>
       <c r="Q32">
-        <v>24.32369875</v>
+        <v>24.206155375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1205027060722272</v>
+        <v>0.1213805287052734</v>
       </c>
       <c r="T32">
-        <v>1.456094785421402</v>
+        <v>1.473205182429879</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.105236683904984</v>
+        <v>3.005067758617726</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09865581480663864</v>
+        <v>0.1004092353627182</v>
       </c>
       <c r="C33">
-        <v>171.1509194496213</v>
+        <v>161.7080032045328</v>
       </c>
       <c r="D33">
-        <v>217.9459194496213</v>
+        <v>210.9480032045328</v>
       </c>
       <c r="E33">
-        <v>22.095</v>
+        <v>24.53999999999999</v>
       </c>
       <c r="F33">
-        <v>75.795</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="G33">
         <v>29</v>
@@ -4124,45 +4124,45 @@
         <v>14.6</v>
       </c>
       <c r="M33">
-        <v>4.8584595</v>
+        <v>5.625456</v>
       </c>
       <c r="N33">
-        <v>9.741540500000001</v>
+        <v>8.974544000000002</v>
       </c>
       <c r="O33">
-        <v>2.435385125</v>
+        <v>2.243636</v>
       </c>
       <c r="P33">
-        <v>7.306155375000001</v>
+        <v>6.730908000000001</v>
       </c>
       <c r="Q33">
-        <v>24.206155375</v>
+        <v>23.630908</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1213805287052734</v>
+        <v>0.1222841696510562</v>
       </c>
       <c r="T33">
-        <v>1.473205182429879</v>
+        <v>1.490818826409194</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.005067758617726</v>
+        <v>2.59534515957462</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1004092353627182</v>
+        <v>0.1003491559187978</v>
       </c>
       <c r="C34">
-        <v>161.7080032045328</v>
+        <v>159.4953374820333</v>
       </c>
       <c r="D34">
-        <v>210.9480032045328</v>
+        <v>211.1803374820333</v>
       </c>
       <c r="E34">
-        <v>24.53999999999999</v>
+        <v>26.985</v>
       </c>
       <c r="F34">
-        <v>78.23999999999999</v>
+        <v>80.685</v>
       </c>
       <c r="G34">
         <v>29</v>
@@ -4206,28 +4206,28 @@
         <v>14.6</v>
       </c>
       <c r="M34">
-        <v>5.625456</v>
+        <v>5.8012515</v>
       </c>
       <c r="N34">
-        <v>8.974544000000002</v>
+        <v>8.798748500000002</v>
       </c>
       <c r="O34">
-        <v>2.243636</v>
+        <v>2.199687125000001</v>
       </c>
       <c r="P34">
-        <v>6.730908000000001</v>
+        <v>6.599061375000002</v>
       </c>
       <c r="Q34">
-        <v>23.630908</v>
+        <v>23.499061375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1222841696510562</v>
+        <v>0.1232147849534295</v>
       </c>
       <c r="T34">
-        <v>1.490818826409194</v>
+        <v>1.508958250805801</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.59534515957462</v>
+        <v>2.516698336557207</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1003491559187978</v>
+        <v>0.1012835764748773</v>
       </c>
       <c r="C35">
-        <v>159.4953374820333</v>
+        <v>153.4937670350581</v>
       </c>
       <c r="D35">
-        <v>211.1803374820333</v>
+        <v>207.6237670350581</v>
       </c>
       <c r="E35">
-        <v>26.985</v>
+        <v>29.43000000000001</v>
       </c>
       <c r="F35">
-        <v>80.685</v>
+        <v>83.13000000000001</v>
       </c>
       <c r="G35">
         <v>29</v>
@@ -4288,45 +4288,45 @@
         <v>14.6</v>
       </c>
       <c r="M35">
-        <v>5.8012515</v>
+        <v>6.301254000000001</v>
       </c>
       <c r="N35">
-        <v>8.798748500000002</v>
+        <v>8.298746000000001</v>
       </c>
       <c r="O35">
-        <v>2.199687125000001</v>
+        <v>2.0746865</v>
       </c>
       <c r="P35">
-        <v>6.599061375000002</v>
+        <v>6.224059500000001</v>
       </c>
       <c r="Q35">
-        <v>23.499061375</v>
+        <v>23.1240595</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1232147849534295</v>
+        <v>0.1241736007195111</v>
       </c>
       <c r="T35">
-        <v>1.508958250805801</v>
+        <v>1.527647354729579</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.516698336557207</v>
+        <v>2.31699912430129</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1012835764748773</v>
+        <v>0.1012527470309569</v>
       </c>
       <c r="C36">
-        <v>153.4937670350581</v>
+        <v>151.1641973000148</v>
       </c>
       <c r="D36">
-        <v>207.6237670350581</v>
+        <v>207.7391973000148</v>
       </c>
       <c r="E36">
-        <v>29.43000000000001</v>
+        <v>31.875</v>
       </c>
       <c r="F36">
-        <v>83.13000000000001</v>
+        <v>85.575</v>
       </c>
       <c r="G36">
         <v>29</v>
@@ -4370,28 +4370,28 @@
         <v>14.6</v>
       </c>
       <c r="M36">
-        <v>6.301254000000001</v>
+        <v>6.486585000000001</v>
       </c>
       <c r="N36">
-        <v>8.298746000000001</v>
+        <v>8.113415</v>
       </c>
       <c r="O36">
-        <v>2.0746865</v>
+        <v>2.02835375</v>
       </c>
       <c r="P36">
-        <v>6.224059500000001</v>
+        <v>6.08506125</v>
       </c>
       <c r="Q36">
-        <v>23.1240595</v>
+        <v>22.98506125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1241736007195111</v>
+        <v>0.1251619185091645</v>
       </c>
       <c r="T36">
-        <v>1.527647354729579</v>
+        <v>1.546911508004857</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.31699912430129</v>
+        <v>2.250799149321253</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1012527470309569</v>
+        <v>0.1012219175870365</v>
       </c>
       <c r="C37">
-        <v>151.1641973000148</v>
+        <v>148.8347559853161</v>
       </c>
       <c r="D37">
-        <v>207.7391973000148</v>
+        <v>207.8547559853161</v>
       </c>
       <c r="E37">
-        <v>31.875</v>
+        <v>34.32000000000001</v>
       </c>
       <c r="F37">
-        <v>85.575</v>
+        <v>88.02000000000001</v>
       </c>
       <c r="G37">
         <v>29</v>
@@ -4452,28 +4452,28 @@
         <v>14.6</v>
       </c>
       <c r="M37">
-        <v>6.486585000000001</v>
+        <v>6.671916000000001</v>
       </c>
       <c r="N37">
-        <v>8.113415</v>
+        <v>7.928084</v>
       </c>
       <c r="O37">
-        <v>2.02835375</v>
+        <v>1.982021</v>
       </c>
       <c r="P37">
-        <v>6.08506125</v>
+        <v>5.946063000000001</v>
       </c>
       <c r="Q37">
-        <v>22.98506125</v>
+        <v>22.846063</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1251619185091645</v>
+        <v>0.1261811212297445</v>
       </c>
       <c r="T37">
-        <v>1.546911508004857</v>
+        <v>1.566777666069988</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.250799149321253</v>
+        <v>2.188276950728996</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1012219175870365</v>
+        <v>0.1011910881431161</v>
       </c>
       <c r="C38">
-        <v>148.8347559853161</v>
+        <v>146.5054433053898</v>
       </c>
       <c r="D38">
-        <v>207.8547559853161</v>
+        <v>207.9704433053898</v>
       </c>
       <c r="E38">
-        <v>34.31999999999999</v>
+        <v>36.765</v>
       </c>
       <c r="F38">
-        <v>88.02</v>
+        <v>90.465</v>
       </c>
       <c r="G38">
         <v>29</v>
@@ -4534,28 +4534,28 @@
         <v>14.6</v>
       </c>
       <c r="M38">
-        <v>6.671916</v>
+        <v>6.857247000000001</v>
       </c>
       <c r="N38">
-        <v>7.928084000000001</v>
+        <v>7.742753</v>
       </c>
       <c r="O38">
-        <v>1.982021</v>
+        <v>1.93568825</v>
       </c>
       <c r="P38">
-        <v>5.946063000000001</v>
+        <v>5.80706475</v>
       </c>
       <c r="Q38">
-        <v>22.846063</v>
+        <v>22.70706475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1261811212297445</v>
+        <v>0.1272326795922477</v>
       </c>
       <c r="T38">
-        <v>1.566777666069988</v>
+        <v>1.587274495819726</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.188276950728996</v>
+        <v>2.129134330439023</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1011910881431161</v>
+        <v>0.1011602586991956</v>
       </c>
       <c r="C39">
-        <v>146.5054433053898</v>
+        <v>144.1762594751413</v>
       </c>
       <c r="D39">
-        <v>207.9704433053898</v>
+        <v>208.0862594751412</v>
       </c>
       <c r="E39">
-        <v>36.765</v>
+        <v>39.20999999999999</v>
       </c>
       <c r="F39">
-        <v>90.465</v>
+        <v>92.91</v>
       </c>
       <c r="G39">
         <v>29</v>
@@ -4616,28 +4616,28 @@
         <v>14.6</v>
       </c>
       <c r="M39">
-        <v>6.857247000000001</v>
+        <v>7.042578000000001</v>
       </c>
       <c r="N39">
-        <v>7.742753</v>
+        <v>7.557422000000001</v>
       </c>
       <c r="O39">
-        <v>1.93568825</v>
+        <v>1.8893555</v>
       </c>
       <c r="P39">
-        <v>5.80706475</v>
+        <v>5.6680665</v>
       </c>
       <c r="Q39">
-        <v>22.70706475</v>
+        <v>22.5680665</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1272326795922477</v>
+        <v>0.128318159192251</v>
       </c>
       <c r="T39">
-        <v>1.587274495819726</v>
+        <v>1.608432513625908</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.129134330439023</v>
+        <v>2.073104479637996</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1011602586991956</v>
+        <v>0.1011294292552752</v>
       </c>
       <c r="C40">
-        <v>144.1762594751413</v>
+        <v>141.8472047099547</v>
       </c>
       <c r="D40">
-        <v>208.0862594751412</v>
+        <v>208.2022047099547</v>
       </c>
       <c r="E40">
-        <v>39.20999999999999</v>
+        <v>41.655</v>
       </c>
       <c r="F40">
-        <v>92.91</v>
+        <v>95.355</v>
       </c>
       <c r="G40">
         <v>29</v>
@@ -4698,28 +4698,28 @@
         <v>14.6</v>
       </c>
       <c r="M40">
-        <v>7.042578000000001</v>
+        <v>7.227909000000001</v>
       </c>
       <c r="N40">
-        <v>7.557422000000001</v>
+        <v>7.372091</v>
       </c>
       <c r="O40">
-        <v>1.8893555</v>
+        <v>1.84302275</v>
       </c>
       <c r="P40">
-        <v>5.6680665</v>
+        <v>5.52906825</v>
       </c>
       <c r="Q40">
-        <v>22.5680665</v>
+        <v>22.42906825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.128318159192251</v>
+        <v>0.1294392282873364</v>
       </c>
       <c r="T40">
-        <v>1.608432513625908</v>
+        <v>1.630284236933931</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.073104479637996</v>
+        <v>2.019947954519073</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1011294292552752</v>
+        <v>0.1053585998113548</v>
       </c>
       <c r="C41">
-        <v>141.8472047099547</v>
+        <v>124.618065447797</v>
       </c>
       <c r="D41">
-        <v>208.2022047099547</v>
+        <v>193.418065447797</v>
       </c>
       <c r="E41">
-        <v>41.655</v>
+        <v>44.10000000000001</v>
       </c>
       <c r="F41">
-        <v>95.355</v>
+        <v>97.80000000000001</v>
       </c>
       <c r="G41">
         <v>29</v>
@@ -4780,45 +4780,45 @@
         <v>14.6</v>
       </c>
       <c r="M41">
-        <v>7.227909000000001</v>
+        <v>8.802000000000001</v>
       </c>
       <c r="N41">
-        <v>7.372091</v>
+        <v>5.798</v>
       </c>
       <c r="O41">
-        <v>1.84302275</v>
+        <v>1.4495</v>
       </c>
       <c r="P41">
-        <v>5.52906825</v>
+        <v>4.3485</v>
       </c>
       <c r="Q41">
-        <v>22.42906825</v>
+        <v>21.2485</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1294392282873364</v>
+        <v>0.1305976663522579</v>
       </c>
       <c r="T41">
-        <v>1.630284236933931</v>
+        <v>1.652864351018889</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.019947954519073</v>
+        <v>1.658713928652579</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1053585998113548</v>
+        <v>0.1054342703674343</v>
       </c>
       <c r="C42">
-        <v>124.618065447797</v>
+        <v>121.9276352198745</v>
       </c>
       <c r="D42">
-        <v>193.418065447797</v>
+        <v>193.1726352198745</v>
       </c>
       <c r="E42">
-        <v>44.10000000000001</v>
+        <v>46.545</v>
       </c>
       <c r="F42">
-        <v>97.80000000000001</v>
+        <v>100.245</v>
       </c>
       <c r="G42">
         <v>29</v>
@@ -4862,28 +4862,28 @@
         <v>14.6</v>
       </c>
       <c r="M42">
-        <v>8.802000000000001</v>
+        <v>9.02205</v>
       </c>
       <c r="N42">
-        <v>5.798</v>
+        <v>5.577950000000001</v>
       </c>
       <c r="O42">
-        <v>1.4495</v>
+        <v>1.3944875</v>
       </c>
       <c r="P42">
-        <v>4.3485</v>
+        <v>4.183462500000001</v>
       </c>
       <c r="Q42">
-        <v>21.2485</v>
+        <v>21.0834625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1305976663522579</v>
+        <v>0.131795373504126</v>
       </c>
       <c r="T42">
-        <v>1.652864351018889</v>
+        <v>1.676209892699947</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.658713928652579</v>
+        <v>1.61825749136837</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1054342703674343</v>
+        <v>0.1055099409235139</v>
       </c>
       <c r="C43">
-        <v>121.9276352198745</v>
+        <v>119.237827060624</v>
       </c>
       <c r="D43">
-        <v>193.1726352198745</v>
+        <v>192.927827060624</v>
       </c>
       <c r="E43">
-        <v>46.545</v>
+        <v>48.99000000000001</v>
       </c>
       <c r="F43">
-        <v>100.245</v>
+        <v>102.69</v>
       </c>
       <c r="G43">
         <v>29</v>
@@ -4944,28 +4944,28 @@
         <v>14.6</v>
       </c>
       <c r="M43">
-        <v>9.02205</v>
+        <v>9.242100000000001</v>
       </c>
       <c r="N43">
-        <v>5.577950000000001</v>
+        <v>5.357900000000001</v>
       </c>
       <c r="O43">
-        <v>1.3944875</v>
+        <v>1.339475</v>
       </c>
       <c r="P43">
-        <v>4.183462500000001</v>
+        <v>4.018425000000001</v>
       </c>
       <c r="Q43">
-        <v>21.0834625</v>
+        <v>20.918425</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.131795373504126</v>
+        <v>0.1330343809026102</v>
       </c>
       <c r="T43">
-        <v>1.676209892699947</v>
+        <v>1.700360453059661</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.61825749136837</v>
+        <v>1.579727551097694</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1055099409235139</v>
+        <v>0.1055856114795935</v>
       </c>
       <c r="C44">
-        <v>119.237827060624</v>
+        <v>116.5486386079913</v>
       </c>
       <c r="D44">
-        <v>192.927827060624</v>
+        <v>192.6836386079913</v>
       </c>
       <c r="E44">
-        <v>48.98999999999999</v>
+        <v>51.435</v>
       </c>
       <c r="F44">
-        <v>102.69</v>
+        <v>105.135</v>
       </c>
       <c r="G44">
         <v>29</v>
@@ -5026,28 +5026,28 @@
         <v>14.6</v>
       </c>
       <c r="M44">
-        <v>9.242099999999999</v>
+        <v>9.462149999999999</v>
       </c>
       <c r="N44">
-        <v>5.357900000000003</v>
+        <v>5.137850000000002</v>
       </c>
       <c r="O44">
-        <v>1.339475000000001</v>
+        <v>1.284462500000001</v>
       </c>
       <c r="P44">
-        <v>4.018425000000002</v>
+        <v>3.853387500000002</v>
       </c>
       <c r="Q44">
-        <v>20.918425</v>
+        <v>20.7533875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1330343809026102</v>
+        <v>0.1343168622449008</v>
       </c>
       <c r="T44">
-        <v>1.700360453059661</v>
+        <v>1.725358401502173</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.579727551097695</v>
+        <v>1.542989701072167</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1055856114795935</v>
+        <v>0.1056612820356731</v>
       </c>
       <c r="C45">
-        <v>116.5486386079913</v>
+        <v>113.8600675118659</v>
       </c>
       <c r="D45">
-        <v>192.6836386079913</v>
+        <v>192.4400675118659</v>
       </c>
       <c r="E45">
-        <v>51.435</v>
+        <v>53.88</v>
       </c>
       <c r="F45">
-        <v>105.135</v>
+        <v>107.58</v>
       </c>
       <c r="G45">
         <v>29</v>
@@ -5108,28 +5108,28 @@
         <v>14.6</v>
       </c>
       <c r="M45">
-        <v>9.462149999999999</v>
+        <v>9.6822</v>
       </c>
       <c r="N45">
-        <v>5.137850000000002</v>
+        <v>4.917800000000002</v>
       </c>
       <c r="O45">
-        <v>1.284462500000001</v>
+        <v>1.22945</v>
       </c>
       <c r="P45">
-        <v>3.853387500000002</v>
+        <v>3.688350000000001</v>
       </c>
       <c r="Q45">
-        <v>20.7533875</v>
+        <v>20.58835</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1343168622449008</v>
+        <v>0.1356451464922733</v>
       </c>
       <c r="T45">
-        <v>1.725358401502173</v>
+        <v>1.751249133817632</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.542989701072167</v>
+        <v>1.507921753320526</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1056612820356731</v>
+        <v>0.1271045073753236</v>
       </c>
       <c r="C46">
-        <v>113.8600675118659</v>
+        <v>60.6609843097464</v>
       </c>
       <c r="D46">
-        <v>192.4400675118659</v>
+        <v>141.6859843097464</v>
       </c>
       <c r="E46">
-        <v>53.88</v>
+        <v>56.325</v>
       </c>
       <c r="F46">
-        <v>107.58</v>
+        <v>110.025</v>
       </c>
       <c r="G46">
         <v>29</v>
@@ -5190,45 +5190,45 @@
         <v>14.6</v>
       </c>
       <c r="M46">
-        <v>9.6822</v>
+        <v>16.15167</v>
       </c>
       <c r="N46">
-        <v>4.917800000000002</v>
+        <v>-1.551670000000001</v>
       </c>
       <c r="O46">
-        <v>1.22945</v>
+        <v>-0.3879175000000004</v>
       </c>
       <c r="P46">
-        <v>3.688350000000001</v>
+        <v>-1.163752500000001</v>
       </c>
       <c r="Q46">
-        <v>20.58835</v>
+        <v>15.7362475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1356451464922733</v>
+        <v>0.1381326049694488</v>
       </c>
       <c r="T46">
-        <v>1.751249133817632</v>
+        <v>1.799734329441812</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.2259828240671088</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1136257214269484</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.507921753320526</v>
+        <v>0.9039312962684354</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1271045073753236</v>
+        <v>0.1281145073753236</v>
       </c>
       <c r="C47">
-        <v>60.6609843097464</v>
+        <v>56.47749557044861</v>
       </c>
       <c r="D47">
-        <v>141.6859843097464</v>
+        <v>139.9474955704486</v>
       </c>
       <c r="E47">
-        <v>56.325</v>
+        <v>58.77</v>
       </c>
       <c r="F47">
-        <v>110.025</v>
+        <v>112.47</v>
       </c>
       <c r="G47">
         <v>29</v>
@@ -5272,37 +5272,37 @@
         <v>14.6</v>
       </c>
       <c r="M47">
-        <v>16.15167</v>
+        <v>16.510596</v>
       </c>
       <c r="N47">
-        <v>-1.551670000000001</v>
+        <v>-1.910596000000002</v>
       </c>
       <c r="O47">
-        <v>-0.3879175000000004</v>
+        <v>-0.4776490000000004</v>
       </c>
       <c r="P47">
-        <v>-1.163752500000001</v>
+        <v>-1.432947000000001</v>
       </c>
       <c r="Q47">
-        <v>15.7362475</v>
+        <v>15.467053</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1381326049694488</v>
+        <v>0.1398424680244386</v>
       </c>
       <c r="T47">
-        <v>1.799734329441812</v>
+        <v>1.833062742949993</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2259828240671088</v>
+        <v>0.2210701539786934</v>
       </c>
       <c r="W47">
-        <v>0.1136257214269484</v>
+        <v>0.1143469013959278</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9039312962684354</v>
+        <v>0.8842806159147737</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1281145073753236</v>
+        <v>0.1291245073753237</v>
       </c>
       <c r="C48">
-        <v>56.47749557044861</v>
+        <v>52.33615226187699</v>
       </c>
       <c r="D48">
-        <v>139.9474955704486</v>
+        <v>138.251152261877</v>
       </c>
       <c r="E48">
-        <v>58.77</v>
+        <v>61.215</v>
       </c>
       <c r="F48">
-        <v>112.47</v>
+        <v>114.915</v>
       </c>
       <c r="G48">
         <v>29</v>
@@ -5354,37 +5354,37 @@
         <v>14.6</v>
       </c>
       <c r="M48">
-        <v>16.510596</v>
+        <v>16.869522</v>
       </c>
       <c r="N48">
-        <v>-1.910596000000002</v>
+        <v>-2.269522000000002</v>
       </c>
       <c r="O48">
-        <v>-0.4776490000000004</v>
+        <v>-0.5673805000000005</v>
       </c>
       <c r="P48">
-        <v>-1.432947000000001</v>
+        <v>-1.702141500000002</v>
       </c>
       <c r="Q48">
-        <v>15.467053</v>
+        <v>15.1978585</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1398424680244386</v>
+        <v>0.141616854213579</v>
       </c>
       <c r="T48">
-        <v>1.833062742949993</v>
+        <v>1.867648832439616</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2210701539786934</v>
+        <v>0.2163665336812744</v>
       </c>
       <c r="W48">
-        <v>0.1143469013959278</v>
+        <v>0.1150373928555889</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8842806159147737</v>
+        <v>0.8654661347250976</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1291245073753237</v>
+        <v>0.1301345073753237</v>
       </c>
       <c r="C49">
-        <v>52.33615226187699</v>
+        <v>48.23544016809467</v>
       </c>
       <c r="D49">
-        <v>138.251152261877</v>
+        <v>136.5954401680947</v>
       </c>
       <c r="E49">
-        <v>61.215</v>
+        <v>63.66000000000001</v>
       </c>
       <c r="F49">
-        <v>114.915</v>
+        <v>117.36</v>
       </c>
       <c r="G49">
         <v>29</v>
@@ -5436,37 +5436,37 @@
         <v>14.6</v>
       </c>
       <c r="M49">
-        <v>16.869522</v>
+        <v>17.228448</v>
       </c>
       <c r="N49">
-        <v>-2.269522000000002</v>
+        <v>-2.628448000000002</v>
       </c>
       <c r="O49">
-        <v>-0.5673805000000005</v>
+        <v>-0.6571120000000006</v>
       </c>
       <c r="P49">
-        <v>-1.702141500000002</v>
+        <v>-1.971336000000002</v>
       </c>
       <c r="Q49">
-        <v>15.1978585</v>
+        <v>14.928664</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.141616854213579</v>
+        <v>0.1434594860253786</v>
       </c>
       <c r="T49">
-        <v>1.867648832439616</v>
+        <v>1.903565156140378</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2163665336812744</v>
+        <v>0.2118588975629145</v>
       </c>
       <c r="W49">
-        <v>0.1150373928555889</v>
+        <v>0.1156991138377642</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8654661347250976</v>
+        <v>0.847435590251658</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1301345073753236</v>
+        <v>0.1311445073753236</v>
       </c>
       <c r="C50">
-        <v>48.23544016809474</v>
+        <v>44.17391675243947</v>
       </c>
       <c r="D50">
-        <v>136.5954401680947</v>
+        <v>134.9789167524395</v>
       </c>
       <c r="E50">
-        <v>63.66</v>
+        <v>66.10499999999999</v>
       </c>
       <c r="F50">
-        <v>117.36</v>
+        <v>119.805</v>
       </c>
       <c r="G50">
         <v>29</v>
@@ -5518,37 +5518,37 @@
         <v>14.6</v>
       </c>
       <c r="M50">
-        <v>17.228448</v>
+        <v>17.587374</v>
       </c>
       <c r="N50">
-        <v>-2.628447999999999</v>
+        <v>-2.987373999999999</v>
       </c>
       <c r="O50">
-        <v>-0.6571119999999997</v>
+        <v>-0.7468434999999998</v>
       </c>
       <c r="P50">
-        <v>-1.971335999999999</v>
+        <v>-2.240530499999999</v>
       </c>
       <c r="Q50">
-        <v>14.928664</v>
+        <v>14.6594695</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1434594860253786</v>
+        <v>0.1453743779082291</v>
       </c>
       <c r="T50">
-        <v>1.903565156140378</v>
+        <v>1.940889963123522</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2118588975629146</v>
+        <v>0.2075352465922428</v>
       </c>
       <c r="W50">
-        <v>0.1156991138377642</v>
+        <v>0.1163338258002588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8474355902516583</v>
+        <v>0.8301409863689714</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1311445073753236</v>
+        <v>0.1321545073753236</v>
       </c>
       <c r="C51">
-        <v>44.17391675243947</v>
+        <v>40.15020696572924</v>
       </c>
       <c r="D51">
-        <v>134.9789167524395</v>
+        <v>133.4002069657292</v>
       </c>
       <c r="E51">
-        <v>66.10499999999999</v>
+        <v>68.55</v>
       </c>
       <c r="F51">
-        <v>119.805</v>
+        <v>122.25</v>
       </c>
       <c r="G51">
         <v>29</v>
@@ -5600,37 +5600,37 @@
         <v>14.6</v>
       </c>
       <c r="M51">
-        <v>17.587374</v>
+        <v>17.9463</v>
       </c>
       <c r="N51">
-        <v>-2.987373999999999</v>
+        <v>-3.346299999999999</v>
       </c>
       <c r="O51">
-        <v>-0.7468434999999998</v>
+        <v>-0.8365749999999998</v>
       </c>
       <c r="P51">
-        <v>-2.240530499999999</v>
+        <v>-2.509725</v>
       </c>
       <c r="Q51">
-        <v>14.6594695</v>
+        <v>14.390275</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1453743779082291</v>
+        <v>0.1473658654663937</v>
       </c>
       <c r="T51">
-        <v>1.940889963123522</v>
+        <v>1.979707762385993</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2075352465922428</v>
+        <v>0.203384541660398</v>
       </c>
       <c r="W51">
-        <v>0.1163338258002588</v>
+        <v>0.1169431492842536</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8301409863689714</v>
+        <v>0.813538166641592</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1321545073753236</v>
+        <v>0.1622505114644106</v>
       </c>
       <c r="C52">
-        <v>40.15020696572924</v>
+        <v>3.228645859747047</v>
       </c>
       <c r="D52">
-        <v>133.4002069657292</v>
+        <v>98.92364585974705</v>
       </c>
       <c r="E52">
-        <v>68.55</v>
+        <v>70.995</v>
       </c>
       <c r="F52">
-        <v>122.25</v>
+        <v>124.695</v>
       </c>
       <c r="G52">
         <v>29</v>
@@ -5682,45 +5682,45 @@
         <v>14.6</v>
       </c>
       <c r="M52">
-        <v>17.9463</v>
+        <v>25.038756</v>
       </c>
       <c r="N52">
-        <v>-3.346299999999999</v>
+        <v>-10.438756</v>
       </c>
       <c r="O52">
-        <v>-0.8365749999999998</v>
+        <v>-2.609689</v>
       </c>
       <c r="P52">
-        <v>-2.509725</v>
+        <v>-7.829067000000001</v>
       </c>
       <c r="Q52">
-        <v>14.390275</v>
+        <v>9.070932999999997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1473658654663937</v>
+        <v>0.1525937486169057</v>
       </c>
       <c r="T52">
-        <v>1.979707762385993</v>
+        <v>2.081608935643263</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.203384541660398</v>
+        <v>0.145774015290536</v>
       </c>
       <c r="W52">
-        <v>0.1169431492842536</v>
+        <v>0.1715285777296604</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.813538166641592</v>
+        <v>0.583096061162144</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1622505114644106</v>
+        <v>0.1638005114644106</v>
       </c>
       <c r="C53">
-        <v>3.228645859747047</v>
+        <v>-0.5157692798971141</v>
       </c>
       <c r="D53">
-        <v>98.92364585974705</v>
+        <v>97.62423072010289</v>
       </c>
       <c r="E53">
-        <v>70.995</v>
+        <v>73.44</v>
       </c>
       <c r="F53">
-        <v>124.695</v>
+        <v>127.14</v>
       </c>
       <c r="G53">
         <v>29</v>
@@ -5764,37 +5764,37 @@
         <v>14.6</v>
       </c>
       <c r="M53">
-        <v>25.038756</v>
+        <v>25.529712</v>
       </c>
       <c r="N53">
-        <v>-10.438756</v>
+        <v>-10.929712</v>
       </c>
       <c r="O53">
-        <v>-2.609689</v>
+        <v>-2.732428</v>
       </c>
       <c r="P53">
-        <v>-7.829067000000001</v>
+        <v>-8.197284</v>
       </c>
       <c r="Q53">
-        <v>9.070932999999997</v>
+        <v>8.702715999999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1525937486169057</v>
+        <v>0.1548186183797579</v>
       </c>
       <c r="T53">
-        <v>2.081608935643263</v>
+        <v>2.124975788469164</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.145774015290536</v>
+        <v>0.1429706688426411</v>
       </c>
       <c r="W53">
-        <v>0.1715285777296604</v>
+        <v>0.1720914896963977</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.583096061162144</v>
+        <v>0.5718826753705644</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1638005114644106</v>
+        <v>0.1653505114644106</v>
       </c>
       <c r="C54">
-        <v>-0.5157692798971141</v>
+        <v>-4.226489984581903</v>
       </c>
       <c r="D54">
-        <v>97.62423072010289</v>
+        <v>96.3585100154181</v>
       </c>
       <c r="E54">
-        <v>73.44</v>
+        <v>75.88500000000001</v>
       </c>
       <c r="F54">
-        <v>127.14</v>
+        <v>129.585</v>
       </c>
       <c r="G54">
         <v>29</v>
@@ -5846,37 +5846,37 @@
         <v>14.6</v>
       </c>
       <c r="M54">
-        <v>25.529712</v>
+        <v>26.020668</v>
       </c>
       <c r="N54">
-        <v>-10.929712</v>
+        <v>-11.420668</v>
       </c>
       <c r="O54">
-        <v>-2.732428</v>
+        <v>-2.855167000000001</v>
       </c>
       <c r="P54">
-        <v>-8.197284</v>
+        <v>-8.565501000000001</v>
       </c>
       <c r="Q54">
-        <v>8.702715999999999</v>
+        <v>8.334498999999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1548186183797579</v>
+        <v>0.1571381634516676</v>
       </c>
       <c r="T54">
-        <v>2.124975788469164</v>
+        <v>2.170188039287657</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1429706688426411</v>
+        <v>0.1402731090531573</v>
       </c>
       <c r="W54">
-        <v>0.1720914896963977</v>
+        <v>0.172633159702126</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5718826753705644</v>
+        <v>0.5610924362126291</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1653505114644106</v>
+        <v>0.1669005114644106</v>
       </c>
       <c r="C55">
-        <v>-4.226489984581903</v>
+        <v>-7.904810048368688</v>
       </c>
       <c r="D55">
-        <v>96.3585100154181</v>
+        <v>95.12518995163131</v>
       </c>
       <c r="E55">
-        <v>75.88500000000001</v>
+        <v>78.33</v>
       </c>
       <c r="F55">
-        <v>129.585</v>
+        <v>132.03</v>
       </c>
       <c r="G55">
         <v>29</v>
@@ -5928,37 +5928,37 @@
         <v>14.6</v>
       </c>
       <c r="M55">
-        <v>26.020668</v>
+        <v>26.511624</v>
       </c>
       <c r="N55">
-        <v>-11.420668</v>
+        <v>-11.911624</v>
       </c>
       <c r="O55">
-        <v>-2.855167000000001</v>
+        <v>-2.977906</v>
       </c>
       <c r="P55">
-        <v>-8.565501000000001</v>
+        <v>-8.933717999999999</v>
       </c>
       <c r="Q55">
-        <v>8.334498999999997</v>
+        <v>7.966282</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1571381634516676</v>
+        <v>0.1595585583093126</v>
       </c>
       <c r="T55">
-        <v>2.170188039287657</v>
+        <v>2.217366040141736</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1402731090531573</v>
+        <v>0.1376754588855062</v>
       </c>
       <c r="W55">
-        <v>0.172633159702126</v>
+        <v>0.1731547678557903</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5610924362126291</v>
+        <v>0.5507018355420249</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1669005114644106</v>
+        <v>0.1684505114644106</v>
       </c>
       <c r="C56">
-        <v>-7.904810048368688</v>
+        <v>-11.55195786385343</v>
       </c>
       <c r="D56">
-        <v>95.12518995163131</v>
+        <v>93.92304213614659</v>
       </c>
       <c r="E56">
-        <v>78.33</v>
+        <v>80.77500000000002</v>
       </c>
       <c r="F56">
-        <v>132.03</v>
+        <v>134.475</v>
       </c>
       <c r="G56">
         <v>29</v>
@@ -6010,37 +6010,37 @@
         <v>14.6</v>
       </c>
       <c r="M56">
-        <v>26.511624</v>
+        <v>27.00258000000001</v>
       </c>
       <c r="N56">
-        <v>-11.911624</v>
+        <v>-12.40258</v>
       </c>
       <c r="O56">
-        <v>-2.977906</v>
+        <v>-3.100645000000001</v>
       </c>
       <c r="P56">
-        <v>-8.933717999999999</v>
+        <v>-9.301935000000004</v>
       </c>
       <c r="Q56">
-        <v>7.966282</v>
+        <v>7.598064999999995</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1595585583093126</v>
+        <v>0.1620865262717418</v>
       </c>
       <c r="T56">
-        <v>2.217366040141736</v>
+        <v>2.266640841033775</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1376754588855062</v>
+        <v>0.1351722687239515</v>
       </c>
       <c r="W56">
-        <v>0.1731547678557903</v>
+        <v>0.1736574084402305</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5507018355420249</v>
+        <v>0.5406890748958062</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1684505114644106</v>
+        <v>0.1700005114644106</v>
       </c>
       <c r="C57">
-        <v>-11.55195786385343</v>
+        <v>-15.16910050315926</v>
       </c>
       <c r="D57">
-        <v>93.92304213614659</v>
+        <v>92.75089949684076</v>
       </c>
       <c r="E57">
-        <v>80.77500000000002</v>
+        <v>83.22000000000001</v>
       </c>
       <c r="F57">
-        <v>134.475</v>
+        <v>136.92</v>
       </c>
       <c r="G57">
         <v>29</v>
@@ -6092,37 +6092,37 @@
         <v>14.6</v>
       </c>
       <c r="M57">
-        <v>27.00258000000001</v>
+        <v>27.493536</v>
       </c>
       <c r="N57">
-        <v>-12.40258</v>
+        <v>-12.893536</v>
       </c>
       <c r="O57">
-        <v>-3.100645000000001</v>
+        <v>-3.223384</v>
       </c>
       <c r="P57">
-        <v>-9.301935000000004</v>
+        <v>-9.670152000000002</v>
       </c>
       <c r="Q57">
-        <v>7.598064999999995</v>
+        <v>7.229847999999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1620865262717418</v>
+        <v>0.1647294018688268</v>
       </c>
       <c r="T57">
-        <v>2.266640841033775</v>
+        <v>2.318155405602724</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1351722687239515</v>
+        <v>0.1327584782110239</v>
       </c>
       <c r="W57">
-        <v>0.1736574084402305</v>
+        <v>0.1741420975752264</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5406890748958062</v>
+        <v>0.5310339128440955</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1700005114644106</v>
+        <v>0.1715505114644106</v>
       </c>
       <c r="C58">
-        <v>-15.16910050315926</v>
+        <v>-18.75734749711513</v>
       </c>
       <c r="D58">
-        <v>92.75089949684076</v>
+        <v>91.60765250288487</v>
       </c>
       <c r="E58">
-        <v>83.22000000000001</v>
+        <v>85.66500000000001</v>
       </c>
       <c r="F58">
-        <v>136.92</v>
+        <v>139.365</v>
       </c>
       <c r="G58">
         <v>29</v>
@@ -6174,37 +6174,37 @@
         <v>14.6</v>
       </c>
       <c r="M58">
-        <v>27.493536</v>
+        <v>27.984492</v>
       </c>
       <c r="N58">
-        <v>-12.893536</v>
+        <v>-13.384492</v>
       </c>
       <c r="O58">
-        <v>-3.223384</v>
+        <v>-3.346123</v>
       </c>
       <c r="P58">
-        <v>-9.670152000000002</v>
+        <v>-10.038369</v>
       </c>
       <c r="Q58">
-        <v>7.229847999999997</v>
+        <v>6.861630999999997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1647294018688268</v>
+        <v>0.1674952019122879</v>
       </c>
       <c r="T58">
-        <v>2.318155405602724</v>
+        <v>2.372065996430695</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1327584782110239</v>
+        <v>0.1304293821020585</v>
       </c>
       <c r="W58">
-        <v>0.1741420975752264</v>
+        <v>0.1746097800739067</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5310339128440955</v>
+        <v>0.521717528408234</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1715505114644106</v>
+        <v>0.1731005114644106</v>
       </c>
       <c r="C59">
-        <v>-18.75734749711513</v>
+        <v>-22.31775433834507</v>
       </c>
       <c r="D59">
-        <v>91.60765250288487</v>
+        <v>90.49224566165496</v>
       </c>
       <c r="E59">
-        <v>85.66500000000001</v>
+        <v>88.11000000000003</v>
       </c>
       <c r="F59">
-        <v>139.365</v>
+        <v>141.81</v>
       </c>
       <c r="G59">
         <v>29</v>
@@ -6256,37 +6256,37 @@
         <v>14.6</v>
       </c>
       <c r="M59">
-        <v>27.984492</v>
+        <v>28.47544800000001</v>
       </c>
       <c r="N59">
-        <v>-13.384492</v>
+        <v>-13.87544800000001</v>
       </c>
       <c r="O59">
-        <v>-3.346123</v>
+        <v>-3.468862000000001</v>
       </c>
       <c r="P59">
-        <v>-10.038369</v>
+        <v>-10.406586</v>
       </c>
       <c r="Q59">
-        <v>6.861630999999997</v>
+        <v>6.493413999999994</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1674952019122879</v>
+        <v>0.1703927067197233</v>
       </c>
       <c r="T59">
-        <v>2.372065996430695</v>
+        <v>2.428543758250473</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1304293821020585</v>
+        <v>0.128180599652023</v>
       </c>
       <c r="W59">
-        <v>0.1746097800739067</v>
+        <v>0.1750613355898738</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.521717528408234</v>
+        <v>0.512722398608092</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1731005114644106</v>
+        <v>0.1746505114644106</v>
       </c>
       <c r="C60">
-        <v>-22.31775433834504</v>
+        <v>-25.85132573151569</v>
       </c>
       <c r="D60">
-        <v>90.49224566165496</v>
+        <v>89.40367426848431</v>
       </c>
       <c r="E60">
-        <v>88.11</v>
+        <v>90.55499999999999</v>
       </c>
       <c r="F60">
-        <v>141.81</v>
+        <v>144.255</v>
       </c>
       <c r="G60">
         <v>29</v>
@@ -6338,37 +6338,37 @@
         <v>14.6</v>
       </c>
       <c r="M60">
-        <v>28.475448</v>
+        <v>28.966404</v>
       </c>
       <c r="N60">
-        <v>-13.875448</v>
+        <v>-14.366404</v>
       </c>
       <c r="O60">
-        <v>-3.468862</v>
+        <v>-3.591601</v>
       </c>
       <c r="P60">
-        <v>-10.406586</v>
+        <v>-10.774803</v>
       </c>
       <c r="Q60">
-        <v>6.493414</v>
+        <v>6.125197</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1703927067197233</v>
+        <v>0.1734315532250824</v>
       </c>
       <c r="T60">
-        <v>2.428543758250473</v>
+        <v>2.487776532841948</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1281805996520231</v>
+        <v>0.1260080471155481</v>
       </c>
       <c r="W60">
-        <v>0.1750613355898738</v>
+        <v>0.175497584139198</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5127223986080922</v>
+        <v>0.5040321884621923</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1746505114644106</v>
+        <v>0.1978243427880157</v>
       </c>
       <c r="C61">
-        <v>-25.85132573151569</v>
+        <v>-41.92457518954733</v>
       </c>
       <c r="D61">
-        <v>89.40367426848431</v>
+        <v>75.77542481045266</v>
       </c>
       <c r="E61">
-        <v>90.55499999999999</v>
+        <v>92.99999999999999</v>
       </c>
       <c r="F61">
-        <v>144.255</v>
+        <v>146.7</v>
       </c>
       <c r="G61">
         <v>29</v>
@@ -6420,45 +6420,45 @@
         <v>14.6</v>
       </c>
       <c r="M61">
-        <v>28.966404</v>
+        <v>34.59186</v>
       </c>
       <c r="N61">
-        <v>-14.366404</v>
+        <v>-19.99186</v>
       </c>
       <c r="O61">
-        <v>-3.591601</v>
+        <v>-4.997964999999999</v>
       </c>
       <c r="P61">
-        <v>-10.774803</v>
+        <v>-14.993895</v>
       </c>
       <c r="Q61">
-        <v>6.125197</v>
+        <v>1.906105000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1734315532250824</v>
+        <v>0.1781819203647223</v>
       </c>
       <c r="T61">
-        <v>2.487776532841948</v>
+        <v>2.580370030247236</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1260080471155481</v>
+        <v>0.1055161532221743</v>
       </c>
       <c r="W61">
-        <v>0.175497584139198</v>
+        <v>0.2109192910702113</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5040321884621923</v>
+        <v>0.422064612888697</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1978243427880157</v>
+        <v>0.1997243427880157</v>
       </c>
       <c r="C62">
-        <v>-41.92457518954733</v>
+        <v>-45.30492631421086</v>
       </c>
       <c r="D62">
-        <v>75.77542481045266</v>
+        <v>74.84007368578915</v>
       </c>
       <c r="E62">
-        <v>92.99999999999999</v>
+        <v>95.44500000000001</v>
       </c>
       <c r="F62">
-        <v>146.7</v>
+        <v>149.145</v>
       </c>
       <c r="G62">
         <v>29</v>
@@ -6502,37 +6502,37 @@
         <v>14.6</v>
       </c>
       <c r="M62">
-        <v>34.59186</v>
+        <v>35.16839100000001</v>
       </c>
       <c r="N62">
-        <v>-19.99186</v>
+        <v>-20.56839100000001</v>
       </c>
       <c r="O62">
-        <v>-4.997964999999999</v>
+        <v>-5.142097750000001</v>
       </c>
       <c r="P62">
-        <v>-14.993895</v>
+        <v>-15.42629325</v>
       </c>
       <c r="Q62">
-        <v>1.906105000000002</v>
+        <v>1.473706749999995</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1781819203647223</v>
+        <v>0.1815763285792023</v>
       </c>
       <c r="T62">
-        <v>2.580370030247236</v>
+        <v>2.646533364356139</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1055161532221743</v>
+        <v>0.103786380218532</v>
       </c>
       <c r="W62">
-        <v>0.2109192910702113</v>
+        <v>0.2113271715444701</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.422064612888697</v>
+        <v>0.4151455208741281</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1997243427880157</v>
+        <v>0.2016243427880157</v>
       </c>
       <c r="C63">
-        <v>-45.30492631421086</v>
+        <v>-48.662467560712</v>
       </c>
       <c r="D63">
-        <v>74.84007368578915</v>
+        <v>73.927532439288</v>
       </c>
       <c r="E63">
-        <v>95.44500000000001</v>
+        <v>97.89</v>
       </c>
       <c r="F63">
-        <v>149.145</v>
+        <v>151.59</v>
       </c>
       <c r="G63">
         <v>29</v>
@@ -6584,37 +6584,37 @@
         <v>14.6</v>
       </c>
       <c r="M63">
-        <v>35.16839100000001</v>
+        <v>35.744922</v>
       </c>
       <c r="N63">
-        <v>-20.56839100000001</v>
+        <v>-21.144922</v>
       </c>
       <c r="O63">
-        <v>-5.142097750000001</v>
+        <v>-5.2862305</v>
       </c>
       <c r="P63">
-        <v>-15.42629325</v>
+        <v>-15.8586915</v>
       </c>
       <c r="Q63">
-        <v>1.473706749999995</v>
+        <v>1.041308499999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1815763285792023</v>
+        <v>0.1851493898576024</v>
       </c>
       <c r="T63">
-        <v>2.646533364356139</v>
+        <v>2.716178979207617</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.103786380218532</v>
+        <v>0.1021124063440396</v>
       </c>
       <c r="W63">
-        <v>0.2113271715444701</v>
+        <v>0.2117218945840755</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4151455208741281</v>
+        <v>0.4084496253761584</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2016243427880157</v>
+        <v>0.2035243427880157</v>
       </c>
       <c r="C64">
-        <v>-48.662467560712</v>
+        <v>-51.99802325523423</v>
       </c>
       <c r="D64">
-        <v>73.927532439288</v>
+        <v>73.03697674476577</v>
       </c>
       <c r="E64">
-        <v>97.89</v>
+        <v>100.335</v>
       </c>
       <c r="F64">
-        <v>151.59</v>
+        <v>154.035</v>
       </c>
       <c r="G64">
         <v>29</v>
@@ -6666,37 +6666,37 @@
         <v>14.6</v>
       </c>
       <c r="M64">
-        <v>35.744922</v>
+        <v>36.321453</v>
       </c>
       <c r="N64">
-        <v>-21.144922</v>
+        <v>-21.721453</v>
       </c>
       <c r="O64">
-        <v>-5.2862305</v>
+        <v>-5.430363249999999</v>
       </c>
       <c r="P64">
-        <v>-15.8586915</v>
+        <v>-16.29108975</v>
       </c>
       <c r="Q64">
-        <v>1.041308499999998</v>
+        <v>0.608910250000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1851493898576024</v>
+        <v>0.1889155895834835</v>
       </c>
       <c r="T64">
-        <v>2.716178979207617</v>
+        <v>2.789589221888904</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1021124063440396</v>
+        <v>0.1004915744973088</v>
       </c>
       <c r="W64">
-        <v>0.2117218945840755</v>
+        <v>0.2121040867335346</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4084496253761584</v>
+        <v>0.4019662979892352</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2035243427880157</v>
+        <v>0.2054243427880157</v>
       </c>
       <c r="C65">
-        <v>-51.99802325523423</v>
+        <v>-55.31237847631944</v>
       </c>
       <c r="D65">
-        <v>73.03697674476577</v>
+        <v>72.16762152368055</v>
       </c>
       <c r="E65">
-        <v>100.335</v>
+        <v>102.78</v>
       </c>
       <c r="F65">
-        <v>154.035</v>
+        <v>156.48</v>
       </c>
       <c r="G65">
         <v>29</v>
@@ -6748,37 +6748,37 @@
         <v>14.6</v>
       </c>
       <c r="M65">
-        <v>36.321453</v>
+        <v>36.897984</v>
       </c>
       <c r="N65">
-        <v>-21.721453</v>
+        <v>-22.297984</v>
       </c>
       <c r="O65">
-        <v>-5.430363249999999</v>
+        <v>-5.574496</v>
       </c>
       <c r="P65">
-        <v>-16.29108975</v>
+        <v>-16.723488</v>
       </c>
       <c r="Q65">
-        <v>0.608910250000001</v>
+        <v>0.1765119999999989</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1889155895834835</v>
+        <v>0.1928910226274692</v>
       </c>
       <c r="T65">
-        <v>2.789589221888904</v>
+        <v>2.867077811385818</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1004915744973088</v>
+        <v>0.09892139364578835</v>
       </c>
       <c r="W65">
-        <v>0.2121040867335346</v>
+        <v>0.2124743353783231</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4019662979892352</v>
+        <v>0.3956855745831535</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2054243427880157</v>
+        <v>0.2073243427880157</v>
       </c>
       <c r="C66">
-        <v>-55.31237847631944</v>
+        <v>-58.60628136320472</v>
       </c>
       <c r="D66">
-        <v>72.16762152368055</v>
+        <v>71.3187186367953</v>
       </c>
       <c r="E66">
-        <v>102.78</v>
+        <v>105.225</v>
       </c>
       <c r="F66">
-        <v>156.48</v>
+        <v>158.925</v>
       </c>
       <c r="G66">
         <v>29</v>
@@ -6830,37 +6830,37 @@
         <v>14.6</v>
       </c>
       <c r="M66">
-        <v>36.897984</v>
+        <v>37.474515</v>
       </c>
       <c r="N66">
-        <v>-22.297984</v>
+        <v>-22.874515</v>
       </c>
       <c r="O66">
-        <v>-5.574496</v>
+        <v>-5.718628750000001</v>
       </c>
       <c r="P66">
-        <v>-16.723488</v>
+        <v>-17.15588625</v>
       </c>
       <c r="Q66">
-        <v>0.1765119999999989</v>
+        <v>-0.2558862500000032</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1928910226274692</v>
+        <v>0.1970936232739683</v>
       </c>
       <c r="T66">
-        <v>2.867077811385818</v>
+        <v>2.948994320282556</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09892139364578835</v>
+        <v>0.09739952605123775</v>
       </c>
       <c r="W66">
-        <v>0.2124743353783231</v>
+        <v>0.2128331917571182</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3956855745831535</v>
+        <v>0.389598104204951</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2073243427880157</v>
+        <v>0.2092243427880157</v>
       </c>
       <c r="C67">
-        <v>-58.60628136320472</v>
+        <v>-61.88044526313658</v>
       </c>
       <c r="D67">
-        <v>71.3187186367953</v>
+        <v>70.48955473686343</v>
       </c>
       <c r="E67">
-        <v>105.225</v>
+        <v>107.67</v>
       </c>
       <c r="F67">
-        <v>158.925</v>
+        <v>161.37</v>
       </c>
       <c r="G67">
         <v>29</v>
@@ -6912,37 +6912,37 @@
         <v>14.6</v>
       </c>
       <c r="M67">
-        <v>37.474515</v>
+        <v>38.051046</v>
       </c>
       <c r="N67">
-        <v>-22.874515</v>
+        <v>-23.451046</v>
       </c>
       <c r="O67">
-        <v>-5.718628750000001</v>
+        <v>-5.8627615</v>
       </c>
       <c r="P67">
-        <v>-17.15588625</v>
+        <v>-17.5882845</v>
       </c>
       <c r="Q67">
-        <v>-0.2558862500000032</v>
+        <v>-0.6882845000000017</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1970936232739683</v>
+        <v>0.2015434357232027</v>
       </c>
       <c r="T67">
-        <v>2.948994320282556</v>
+        <v>3.035729447349689</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09739952605123775</v>
+        <v>0.09592377565652205</v>
       </c>
       <c r="W67">
-        <v>0.2128331917571182</v>
+        <v>0.2131811737001921</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.389598104204951</v>
+        <v>0.3836951026260882</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2092243427880157</v>
+        <v>0.2111243427880157</v>
       </c>
       <c r="C68">
-        <v>-61.88044526313658</v>
+        <v>-65.13555073061617</v>
       </c>
       <c r="D68">
-        <v>70.48955473686343</v>
+        <v>69.67944926938382</v>
       </c>
       <c r="E68">
-        <v>107.67</v>
+        <v>110.115</v>
       </c>
       <c r="F68">
-        <v>161.37</v>
+        <v>163.815</v>
       </c>
       <c r="G68">
         <v>29</v>
@@ -6994,37 +6994,37 @@
         <v>14.6</v>
       </c>
       <c r="M68">
-        <v>38.051046</v>
+        <v>38.627577</v>
       </c>
       <c r="N68">
-        <v>-23.451046</v>
+        <v>-24.027577</v>
       </c>
       <c r="O68">
-        <v>-5.8627615</v>
+        <v>-6.00689425</v>
       </c>
       <c r="P68">
-        <v>-17.5882845</v>
+        <v>-18.02068275</v>
       </c>
       <c r="Q68">
-        <v>-0.6882845000000017</v>
+        <v>-1.12068275</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2015434357232027</v>
+        <v>0.2062629337754209</v>
       </c>
       <c r="T68">
-        <v>3.035729447349689</v>
+        <v>3.127721248784529</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09592377565652205</v>
+        <v>0.09449207751239484</v>
       </c>
       <c r="W68">
-        <v>0.2131811737001921</v>
+        <v>0.2135187681225773</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3836951026260882</v>
+        <v>0.3779683100495793</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2111243427880157</v>
+        <v>0.2130243427880157</v>
       </c>
       <c r="C69">
-        <v>-65.13555073061617</v>
+        <v>-68.37224739035223</v>
       </c>
       <c r="D69">
-        <v>69.67944926938382</v>
+        <v>68.88775260964779</v>
       </c>
       <c r="E69">
-        <v>110.115</v>
+        <v>112.56</v>
       </c>
       <c r="F69">
-        <v>163.815</v>
+        <v>166.26</v>
       </c>
       <c r="G69">
         <v>29</v>
@@ -7076,37 +7076,37 @@
         <v>14.6</v>
       </c>
       <c r="M69">
-        <v>38.627577</v>
+        <v>39.20410800000001</v>
       </c>
       <c r="N69">
-        <v>-24.027577</v>
+        <v>-24.604108</v>
       </c>
       <c r="O69">
-        <v>-6.00689425</v>
+        <v>-6.151027000000001</v>
       </c>
       <c r="P69">
-        <v>-18.02068275</v>
+        <v>-18.453081</v>
       </c>
       <c r="Q69">
-        <v>-1.12068275</v>
+        <v>-1.553081000000006</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2062629337754209</v>
+        <v>0.2112774004559028</v>
       </c>
       <c r="T69">
-        <v>3.127721248784529</v>
+        <v>3.225462537809045</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09449207751239484</v>
+        <v>0.09310248813721256</v>
       </c>
       <c r="W69">
-        <v>0.2135187681225773</v>
+        <v>0.2138464332972453</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3779683100495793</v>
+        <v>0.3724099525488502</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2130243427880157</v>
+        <v>0.2149243427880157</v>
       </c>
       <c r="C70">
-        <v>-68.37224739035223</v>
+        <v>-71.59115567463978</v>
       </c>
       <c r="D70">
-        <v>68.88775260964779</v>
+        <v>68.11384432536023</v>
       </c>
       <c r="E70">
-        <v>112.56</v>
+        <v>115.005</v>
       </c>
       <c r="F70">
-        <v>166.26</v>
+        <v>168.705</v>
       </c>
       <c r="G70">
         <v>29</v>
@@ -7158,37 +7158,37 @@
         <v>14.6</v>
       </c>
       <c r="M70">
-        <v>39.20410800000001</v>
+        <v>39.78063900000001</v>
       </c>
       <c r="N70">
-        <v>-24.604108</v>
+        <v>-25.18063900000001</v>
       </c>
       <c r="O70">
-        <v>-6.151027000000001</v>
+        <v>-6.295159750000002</v>
       </c>
       <c r="P70">
-        <v>-18.453081</v>
+        <v>-18.88547925</v>
       </c>
       <c r="Q70">
-        <v>-1.553081000000006</v>
+        <v>-1.985479250000004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2112774004559028</v>
+        <v>0.2166153811157707</v>
       </c>
       <c r="T70">
-        <v>3.225462537809045</v>
+        <v>3.329509716448047</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09310248813721256</v>
+        <v>0.0917531767149341</v>
       </c>
       <c r="W70">
-        <v>0.2138464332972453</v>
+        <v>0.2141646009306185</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3724099525488502</v>
+        <v>0.3670127068597364</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2149243427880157</v>
+        <v>0.2168243427880157</v>
       </c>
       <c r="C71">
-        <v>-71.59115567463978</v>
+        <v>-74.79286844492999</v>
       </c>
       <c r="D71">
-        <v>68.11384432536023</v>
+        <v>67.35713155507001</v>
       </c>
       <c r="E71">
-        <v>115.005</v>
+        <v>117.45</v>
       </c>
       <c r="F71">
-        <v>168.705</v>
+        <v>171.15</v>
       </c>
       <c r="G71">
         <v>29</v>
@@ -7240,37 +7240,37 @@
         <v>14.6</v>
       </c>
       <c r="M71">
-        <v>39.78063900000001</v>
+        <v>40.35717</v>
       </c>
       <c r="N71">
-        <v>-25.18063900000001</v>
+        <v>-25.75717</v>
       </c>
       <c r="O71">
-        <v>-6.295159750000002</v>
+        <v>-6.439292500000001</v>
       </c>
       <c r="P71">
-        <v>-18.88547925</v>
+        <v>-19.3178775</v>
       </c>
       <c r="Q71">
-        <v>-1.985479250000004</v>
+        <v>-2.417877500000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2166153811157707</v>
+        <v>0.2223092271529631</v>
       </c>
       <c r="T71">
-        <v>3.329509716448047</v>
+        <v>3.440493373662982</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0917531767149341</v>
+        <v>0.09044241704757791</v>
       </c>
       <c r="W71">
-        <v>0.2141646009306185</v>
+        <v>0.2144736780601811</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3670127068597364</v>
+        <v>0.3617696681903116</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2168243427880157</v>
+        <v>0.2187243427880157</v>
       </c>
       <c r="C72">
-        <v>-74.79286844492999</v>
+        <v>-77.9779525064986</v>
       </c>
       <c r="D72">
-        <v>67.35713155507001</v>
+        <v>66.61704749350143</v>
       </c>
       <c r="E72">
-        <v>117.45</v>
+        <v>119.895</v>
       </c>
       <c r="F72">
-        <v>171.15</v>
+        <v>173.595</v>
       </c>
       <c r="G72">
         <v>29</v>
@@ -7322,37 +7322,37 @@
         <v>14.6</v>
       </c>
       <c r="M72">
-        <v>40.35717</v>
+        <v>40.93370100000001</v>
       </c>
       <c r="N72">
-        <v>-25.75717</v>
+        <v>-26.333701</v>
       </c>
       <c r="O72">
-        <v>-6.439292500000001</v>
+        <v>-6.583425250000001</v>
       </c>
       <c r="P72">
-        <v>-19.3178775</v>
+        <v>-19.75027575</v>
       </c>
       <c r="Q72">
-        <v>-2.417877500000003</v>
+        <v>-2.850275750000005</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2223092271529631</v>
+        <v>0.2283957522272032</v>
       </c>
       <c r="T72">
-        <v>3.440493373662982</v>
+        <v>3.559131076203085</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09044241704757791</v>
+        <v>0.08916858018775287</v>
       </c>
       <c r="W72">
-        <v>0.2144736780601811</v>
+        <v>0.2147740487917279</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3617696681903116</v>
+        <v>0.3566743207510115</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2187243427880157</v>
+        <v>0.2206243427880157</v>
       </c>
       <c r="C73">
-        <v>-77.97795250649857</v>
+        <v>-81.14695002434496</v>
       </c>
       <c r="D73">
-        <v>66.61704749350143</v>
+        <v>65.89304997565503</v>
       </c>
       <c r="E73">
-        <v>119.895</v>
+        <v>122.34</v>
       </c>
       <c r="F73">
-        <v>173.595</v>
+        <v>176.04</v>
       </c>
       <c r="G73">
         <v>29</v>
@@ -7404,37 +7404,37 @@
         <v>14.6</v>
       </c>
       <c r="M73">
-        <v>40.933701</v>
+        <v>41.510232</v>
       </c>
       <c r="N73">
-        <v>-26.333701</v>
+        <v>-26.910232</v>
       </c>
       <c r="O73">
-        <v>-6.583425249999999</v>
+        <v>-6.727558</v>
       </c>
       <c r="P73">
-        <v>-19.75027575</v>
+        <v>-20.182674</v>
       </c>
       <c r="Q73">
-        <v>-2.850275750000002</v>
+        <v>-3.282674</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2283957522272031</v>
+        <v>0.2349170290924603</v>
       </c>
       <c r="T73">
-        <v>3.559131076203084</v>
+        <v>3.686242900353194</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08916858018775288</v>
+        <v>0.0879301276851452</v>
       </c>
       <c r="W73">
-        <v>0.2147740487917279</v>
+        <v>0.2150660758918428</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3566743207510116</v>
+        <v>0.3517205107405807</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2206243427880157</v>
+        <v>0.2225243427880157</v>
       </c>
       <c r="C74">
-        <v>-81.14695002434496</v>
+        <v>-84.30037984775599</v>
       </c>
       <c r="D74">
-        <v>65.89304997565503</v>
+        <v>65.18462015224399</v>
       </c>
       <c r="E74">
-        <v>122.34</v>
+        <v>124.785</v>
       </c>
       <c r="F74">
-        <v>176.04</v>
+        <v>178.485</v>
       </c>
       <c r="G74">
         <v>29</v>
@@ -7486,37 +7486,37 @@
         <v>14.6</v>
       </c>
       <c r="M74">
-        <v>41.510232</v>
+        <v>42.086763</v>
       </c>
       <c r="N74">
-        <v>-26.910232</v>
+        <v>-27.486763</v>
       </c>
       <c r="O74">
-        <v>-6.727558</v>
+        <v>-6.871690749999999</v>
       </c>
       <c r="P74">
-        <v>-20.182674</v>
+        <v>-20.61507225</v>
       </c>
       <c r="Q74">
-        <v>-3.282674</v>
+        <v>-3.715072249999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2349170290924603</v>
+        <v>0.2419213635032922</v>
       </c>
       <c r="T74">
-        <v>3.686242900353194</v>
+        <v>3.82277041518109</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0879301276851452</v>
+        <v>0.08672560538808842</v>
       </c>
       <c r="W74">
-        <v>0.2150660758918428</v>
+        <v>0.2153501022494888</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3517205107405807</v>
+        <v>0.3469024215523537</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2225243427880157</v>
+        <v>0.2244243427880157</v>
       </c>
       <c r="C75">
-        <v>-84.30037984775599</v>
+        <v>-87.43873875033425</v>
       </c>
       <c r="D75">
-        <v>65.18462015224399</v>
+        <v>64.49126124966575</v>
       </c>
       <c r="E75">
-        <v>124.785</v>
+        <v>127.23</v>
       </c>
       <c r="F75">
-        <v>178.485</v>
+        <v>180.93</v>
       </c>
       <c r="G75">
         <v>29</v>
@@ -7568,37 +7568,37 @@
         <v>14.6</v>
       </c>
       <c r="M75">
-        <v>42.086763</v>
+        <v>42.663294</v>
       </c>
       <c r="N75">
-        <v>-27.486763</v>
+        <v>-28.063294</v>
       </c>
       <c r="O75">
-        <v>-6.871690749999999</v>
+        <v>-7.0158235</v>
       </c>
       <c r="P75">
-        <v>-20.61507225</v>
+        <v>-21.0474705</v>
       </c>
       <c r="Q75">
-        <v>-3.715072249999999</v>
+        <v>-4.147470500000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2419213635032922</v>
+        <v>0.2494644928688035</v>
       </c>
       <c r="T75">
-        <v>3.82277041518109</v>
+        <v>3.969800046534209</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08672560538808842</v>
+        <v>0.08555363774770884</v>
       </c>
       <c r="W75">
-        <v>0.2153501022494888</v>
+        <v>0.2156264522190903</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3469024215523537</v>
+        <v>0.3422145509908354</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2244243427880157</v>
+        <v>0.2263243427880157</v>
       </c>
       <c r="C76">
-        <v>-87.43873875033425</v>
+        <v>-90.56250259171964</v>
       </c>
       <c r="D76">
-        <v>64.49126124966575</v>
+        <v>63.81249740828036</v>
       </c>
       <c r="E76">
-        <v>127.23</v>
+        <v>129.675</v>
       </c>
       <c r="F76">
-        <v>180.93</v>
+        <v>183.375</v>
       </c>
       <c r="G76">
         <v>29</v>
@@ -7650,37 +7650,37 @@
         <v>14.6</v>
       </c>
       <c r="M76">
-        <v>42.663294</v>
+        <v>43.239825</v>
       </c>
       <c r="N76">
-        <v>-28.063294</v>
+        <v>-28.639825</v>
       </c>
       <c r="O76">
-        <v>-7.0158235</v>
+        <v>-7.15995625</v>
       </c>
       <c r="P76">
-        <v>-21.0474705</v>
+        <v>-21.47986875</v>
       </c>
       <c r="Q76">
-        <v>-4.147470500000001</v>
+        <v>-4.579868750000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2494644928688035</v>
+        <v>0.2576110725835556</v>
       </c>
       <c r="T76">
-        <v>3.969800046534209</v>
+        <v>4.128592048395578</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08555363774770884</v>
+        <v>0.08441292257773939</v>
       </c>
       <c r="W76">
-        <v>0.2156264522190903</v>
+        <v>0.2158954328561691</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3422145509908354</v>
+        <v>0.3376516903109575</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2263243427880157</v>
+        <v>0.2282243427880157</v>
       </c>
       <c r="C77">
-        <v>-90.56250259171964</v>
+        <v>-93.67212740671283</v>
       </c>
       <c r="D77">
-        <v>63.81249740828036</v>
+        <v>63.14787259328717</v>
       </c>
       <c r="E77">
-        <v>129.675</v>
+        <v>132.12</v>
       </c>
       <c r="F77">
-        <v>183.375</v>
+        <v>185.82</v>
       </c>
       <c r="G77">
         <v>29</v>
@@ -7732,37 +7732,37 @@
         <v>14.6</v>
       </c>
       <c r="M77">
-        <v>43.239825</v>
+        <v>43.816356</v>
       </c>
       <c r="N77">
-        <v>-28.639825</v>
+        <v>-29.216356</v>
       </c>
       <c r="O77">
-        <v>-7.15995625</v>
+        <v>-7.304088999999999</v>
       </c>
       <c r="P77">
-        <v>-21.47986875</v>
+        <v>-21.912267</v>
       </c>
       <c r="Q77">
-        <v>-4.579868750000003</v>
+        <v>-5.012267000000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2576110725835556</v>
+        <v>0.2664365339412038</v>
       </c>
       <c r="T77">
-        <v>4.128592048395578</v>
+        <v>4.300616717078727</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08441292257773939</v>
+        <v>0.08330222622803229</v>
       </c>
       <c r="W77">
-        <v>0.2158954328561691</v>
+        <v>0.21615733505543</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3376516903109575</v>
+        <v>0.3332089049121292</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2282243427880157</v>
+        <v>0.2301243427880157</v>
       </c>
       <c r="C78">
-        <v>-93.67212740671283</v>
+        <v>-96.76805042703916</v>
       </c>
       <c r="D78">
-        <v>63.14787259328717</v>
+        <v>62.49694957296087</v>
       </c>
       <c r="E78">
-        <v>132.12</v>
+        <v>134.565</v>
       </c>
       <c r="F78">
-        <v>185.82</v>
+        <v>188.265</v>
       </c>
       <c r="G78">
         <v>29</v>
@@ -7814,37 +7814,37 @@
         <v>14.6</v>
       </c>
       <c r="M78">
-        <v>43.816356</v>
+        <v>44.392887</v>
       </c>
       <c r="N78">
-        <v>-29.216356</v>
+        <v>-29.792887</v>
       </c>
       <c r="O78">
-        <v>-7.304088999999999</v>
+        <v>-7.44822175</v>
       </c>
       <c r="P78">
-        <v>-21.912267</v>
+        <v>-22.34466525</v>
       </c>
       <c r="Q78">
-        <v>-5.012267000000001</v>
+        <v>-5.44466525</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2664365339412038</v>
+        <v>0.2760294267212561</v>
       </c>
       <c r="T78">
-        <v>4.300616717078727</v>
+        <v>4.487600052603889</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08330222622803229</v>
+        <v>0.08222037913416175</v>
       </c>
       <c r="W78">
-        <v>0.21615733505543</v>
+        <v>0.2164124346001647</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3332089049121292</v>
+        <v>0.328881516536647</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2301243427880157</v>
+        <v>0.2320243427880157</v>
       </c>
       <c r="C79">
-        <v>-96.76805042703916</v>
+        <v>-99.85069104056407</v>
       </c>
       <c r="D79">
-        <v>62.49694957296087</v>
+        <v>61.85930895943593</v>
       </c>
       <c r="E79">
-        <v>134.565</v>
+        <v>137.01</v>
       </c>
       <c r="F79">
-        <v>188.265</v>
+        <v>190.71</v>
       </c>
       <c r="G79">
         <v>29</v>
@@ -7896,37 +7896,37 @@
         <v>14.6</v>
       </c>
       <c r="M79">
-        <v>44.392887</v>
+        <v>44.969418</v>
       </c>
       <c r="N79">
-        <v>-29.792887</v>
+        <v>-30.369418</v>
       </c>
       <c r="O79">
-        <v>-7.44822175</v>
+        <v>-7.592354500000001</v>
       </c>
       <c r="P79">
-        <v>-22.34466525</v>
+        <v>-22.7770635</v>
       </c>
       <c r="Q79">
-        <v>-5.44466525</v>
+        <v>-5.877063500000006</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2760294267212561</v>
+        <v>0.2864944006631314</v>
       </c>
       <c r="T79">
-        <v>4.487600052603889</v>
+        <v>4.691581873176792</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08222037913416175</v>
+        <v>0.0811662717093648</v>
       </c>
       <c r="W79">
-        <v>0.2164124346001647</v>
+        <v>0.2166609931309318</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.328881516536647</v>
+        <v>0.3246650868374592</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2320243427880157</v>
+        <v>0.2339243427880157</v>
       </c>
       <c r="C80">
-        <v>-99.85069104056407</v>
+        <v>-102.9204516923813</v>
       </c>
       <c r="D80">
-        <v>61.85930895943593</v>
+        <v>61.2345483076187</v>
       </c>
       <c r="E80">
-        <v>137.01</v>
+        <v>139.455</v>
       </c>
       <c r="F80">
-        <v>190.71</v>
+        <v>193.155</v>
       </c>
       <c r="G80">
         <v>29</v>
@@ -7978,37 +7978,37 @@
         <v>14.6</v>
       </c>
       <c r="M80">
-        <v>44.969418</v>
+        <v>45.545949</v>
       </c>
       <c r="N80">
-        <v>-30.369418</v>
+        <v>-30.945949</v>
       </c>
       <c r="O80">
-        <v>-7.592354500000001</v>
+        <v>-7.73648725</v>
       </c>
       <c r="P80">
-        <v>-22.7770635</v>
+        <v>-23.20946175</v>
       </c>
       <c r="Q80">
-        <v>-5.877063500000006</v>
+        <v>-6.309461750000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2864944006631314</v>
+        <v>0.2979560387899472</v>
       </c>
       <c r="T80">
-        <v>4.691581873176792</v>
+        <v>4.91499053380426</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0811662717093648</v>
+        <v>0.08013885054848677</v>
       </c>
       <c r="W80">
-        <v>0.2166609931309318</v>
+        <v>0.2169032590406668</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3246650868374592</v>
+        <v>0.3205554021939471</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2339243427880157</v>
+        <v>0.2358243427880157</v>
       </c>
       <c r="C81">
-        <v>-102.9204516923813</v>
+        <v>-105.9777187318431</v>
       </c>
       <c r="D81">
-        <v>61.2345483076187</v>
+        <v>60.62228126815697</v>
       </c>
       <c r="E81">
-        <v>139.455</v>
+        <v>141.9</v>
       </c>
       <c r="F81">
-        <v>193.155</v>
+        <v>195.6</v>
       </c>
       <c r="G81">
         <v>29</v>
@@ -8060,37 +8060,37 @@
         <v>14.6</v>
       </c>
       <c r="M81">
-        <v>45.545949</v>
+        <v>46.12248000000001</v>
       </c>
       <c r="N81">
-        <v>-30.945949</v>
+        <v>-31.52248000000001</v>
       </c>
       <c r="O81">
-        <v>-7.73648725</v>
+        <v>-7.880620000000002</v>
       </c>
       <c r="P81">
-        <v>-23.20946175</v>
+        <v>-23.64186000000001</v>
       </c>
       <c r="Q81">
-        <v>-6.309461750000001</v>
+        <v>-6.74186000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2979560387899472</v>
+        <v>0.3105638407294446</v>
       </c>
       <c r="T81">
-        <v>4.91499053380426</v>
+        <v>5.160740060494473</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08013885054848677</v>
+        <v>0.07913711491663067</v>
       </c>
       <c r="W81">
-        <v>0.2169032590406668</v>
+        <v>0.2171394683026585</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3205554021939471</v>
+        <v>0.3165484596665227</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2358243427880157</v>
+        <v>0.2377243427880157</v>
       </c>
       <c r="C82">
-        <v>-105.9777187318431</v>
+        <v>-109.0228632092777</v>
       </c>
       <c r="D82">
-        <v>60.62228126815697</v>
+        <v>60.02213679072236</v>
       </c>
       <c r="E82">
-        <v>141.9</v>
+        <v>144.345</v>
       </c>
       <c r="F82">
-        <v>195.6</v>
+        <v>198.045</v>
       </c>
       <c r="G82">
         <v>29</v>
@@ -8142,37 +8142,37 @@
         <v>14.6</v>
       </c>
       <c r="M82">
-        <v>46.12248000000001</v>
+        <v>46.69901100000001</v>
       </c>
       <c r="N82">
-        <v>-31.52248000000001</v>
+        <v>-32.099011</v>
       </c>
       <c r="O82">
-        <v>-7.880620000000002</v>
+        <v>-8.024752750000001</v>
       </c>
       <c r="P82">
-        <v>-23.64186000000001</v>
+        <v>-24.07425825</v>
       </c>
       <c r="Q82">
-        <v>-6.74186000000001</v>
+        <v>-7.174258250000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3105638407294446</v>
+        <v>0.3244987797152048</v>
       </c>
       <c r="T82">
-        <v>5.160740060494473</v>
+        <v>5.432357958415235</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07913711491663067</v>
+        <v>0.07816011349790684</v>
       </c>
       <c r="W82">
-        <v>0.2171394683026585</v>
+        <v>0.2173698452371936</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3165484596665227</v>
+        <v>0.3126404539916273</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2377243427880157</v>
+        <v>0.2396243427880157</v>
       </c>
       <c r="C83">
-        <v>-109.0228632092777</v>
+        <v>-112.0562416258478</v>
       </c>
       <c r="D83">
-        <v>60.02213679072236</v>
+        <v>59.43375837415218</v>
       </c>
       <c r="E83">
-        <v>144.345</v>
+        <v>146.79</v>
       </c>
       <c r="F83">
-        <v>198.045</v>
+        <v>200.49</v>
       </c>
       <c r="G83">
         <v>29</v>
@@ -8224,37 +8224,37 @@
         <v>14.6</v>
       </c>
       <c r="M83">
-        <v>46.69901100000001</v>
+        <v>47.275542</v>
       </c>
       <c r="N83">
-        <v>-32.099011</v>
+        <v>-32.675542</v>
       </c>
       <c r="O83">
-        <v>-8.024752750000001</v>
+        <v>-8.1688855</v>
       </c>
       <c r="P83">
-        <v>-24.07425825</v>
+        <v>-24.5066565</v>
       </c>
       <c r="Q83">
-        <v>-7.174258250000005</v>
+        <v>-7.6066565</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3244987797152048</v>
+        <v>0.3399820452549385</v>
       </c>
       <c r="T83">
-        <v>5.432357958415235</v>
+        <v>5.734155622771637</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07816011349790684</v>
+        <v>0.07720694138207872</v>
       </c>
       <c r="W83">
-        <v>0.2173698452371936</v>
+        <v>0.2175946032221058</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3126404539916273</v>
+        <v>0.3088277655283148</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2396243427880157</v>
+        <v>0.2415243427880157</v>
       </c>
       <c r="C84">
-        <v>-112.0562416258478</v>
+        <v>-115.0781966397329</v>
       </c>
       <c r="D84">
-        <v>59.43375837415218</v>
+        <v>58.85680336026715</v>
       </c>
       <c r="E84">
-        <v>146.79</v>
+        <v>149.235</v>
       </c>
       <c r="F84">
-        <v>200.49</v>
+        <v>202.935</v>
       </c>
       <c r="G84">
         <v>29</v>
@@ -8306,37 +8306,37 @@
         <v>14.6</v>
       </c>
       <c r="M84">
-        <v>47.275542</v>
+        <v>47.85207300000001</v>
       </c>
       <c r="N84">
-        <v>-32.675542</v>
+        <v>-33.25207300000001</v>
       </c>
       <c r="O84">
-        <v>-8.1688855</v>
+        <v>-8.313018250000002</v>
       </c>
       <c r="P84">
-        <v>-24.5066565</v>
+        <v>-24.93905475000001</v>
       </c>
       <c r="Q84">
-        <v>-7.6066565</v>
+        <v>-8.039054750000009</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3399820452549385</v>
+        <v>0.3572868714464054</v>
       </c>
       <c r="T84">
-        <v>5.734155622771637</v>
+        <v>6.07145889469938</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07720694138207872</v>
+        <v>0.07627673726904161</v>
       </c>
       <c r="W84">
-        <v>0.2175946032221058</v>
+        <v>0.21781394535196</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3088277655283148</v>
+        <v>0.3051069490761664</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2415243427880157</v>
+        <v>0.2434243427880157</v>
       </c>
       <c r="C85">
-        <v>-115.0781966397329</v>
+        <v>-118.0890577315745</v>
       </c>
       <c r="D85">
-        <v>58.85680336026715</v>
+        <v>58.29094226842553</v>
       </c>
       <c r="E85">
-        <v>149.235</v>
+        <v>151.68</v>
       </c>
       <c r="F85">
-        <v>202.935</v>
+        <v>205.38</v>
       </c>
       <c r="G85">
         <v>29</v>
@@ -8388,37 +8388,37 @@
         <v>14.6</v>
       </c>
       <c r="M85">
-        <v>47.85207300000001</v>
+        <v>48.42860400000001</v>
       </c>
       <c r="N85">
-        <v>-33.25207300000001</v>
+        <v>-33.82860400000001</v>
       </c>
       <c r="O85">
-        <v>-8.313018250000002</v>
+        <v>-8.457151000000001</v>
       </c>
       <c r="P85">
-        <v>-24.93905475000001</v>
+        <v>-25.371453</v>
       </c>
       <c r="Q85">
-        <v>-8.039054750000009</v>
+        <v>-8.471453000000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3572868714464054</v>
+        <v>0.3767548009118058</v>
       </c>
       <c r="T85">
-        <v>6.07145889469938</v>
+        <v>6.450925075618093</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07627673726904161</v>
+        <v>0.0753686808729816</v>
       </c>
       <c r="W85">
-        <v>0.21781394535196</v>
+        <v>0.2180280650501509</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3051069490761664</v>
+        <v>0.3014747234919264</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2434243427880157</v>
+        <v>0.2453243427880157</v>
       </c>
       <c r="C86">
-        <v>-118.0890577315744</v>
+        <v>-121.0891418319024</v>
       </c>
       <c r="D86">
-        <v>58.29094226842557</v>
+        <v>57.73585816809759</v>
       </c>
       <c r="E86">
-        <v>151.68</v>
+        <v>154.125</v>
       </c>
       <c r="F86">
-        <v>205.38</v>
+        <v>207.825</v>
       </c>
       <c r="G86">
         <v>29</v>
@@ -8470,37 +8470,37 @@
         <v>14.6</v>
       </c>
       <c r="M86">
-        <v>48.428604</v>
+        <v>49.005135</v>
       </c>
       <c r="N86">
-        <v>-33.828604</v>
+        <v>-34.405135</v>
       </c>
       <c r="O86">
-        <v>-8.457151</v>
+        <v>-8.60128375</v>
       </c>
       <c r="P86">
-        <v>-25.371453</v>
+        <v>-25.80385125</v>
       </c>
       <c r="Q86">
-        <v>-8.471453</v>
+        <v>-8.903851250000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3767548009118056</v>
+        <v>0.398818454305926</v>
       </c>
       <c r="T86">
-        <v>6.450925075618088</v>
+        <v>6.880986747325962</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0753686808729816</v>
+        <v>0.07448199050977006</v>
       </c>
       <c r="W86">
-        <v>0.2180280650501509</v>
+        <v>0.2182371466377963</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3014747234919264</v>
+        <v>0.2979279620390802</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2453243427880157</v>
+        <v>0.2472243427880157</v>
       </c>
       <c r="C87">
-        <v>-121.0891418319024</v>
+        <v>-124.0787539130491</v>
       </c>
       <c r="D87">
-        <v>57.73585816809759</v>
+        <v>57.19124608695093</v>
       </c>
       <c r="E87">
-        <v>154.125</v>
+        <v>156.57</v>
       </c>
       <c r="F87">
-        <v>207.825</v>
+        <v>210.27</v>
       </c>
       <c r="G87">
         <v>29</v>
@@ -8552,37 +8552,37 @@
         <v>14.6</v>
       </c>
       <c r="M87">
-        <v>49.005135</v>
+        <v>49.58166600000001</v>
       </c>
       <c r="N87">
-        <v>-34.405135</v>
+        <v>-34.981666</v>
       </c>
       <c r="O87">
-        <v>-8.60128375</v>
+        <v>-8.745416500000001</v>
       </c>
       <c r="P87">
-        <v>-25.80385125</v>
+        <v>-26.2362495</v>
       </c>
       <c r="Q87">
-        <v>-8.903851250000002</v>
+        <v>-9.336249500000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.398818454305926</v>
+        <v>0.4240340581849207</v>
       </c>
       <c r="T87">
-        <v>6.880986747325962</v>
+        <v>7.372485800706388</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07448199050977006</v>
+        <v>0.07361592085267969</v>
       </c>
       <c r="W87">
-        <v>0.2182371466377963</v>
+        <v>0.2184413658629381</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2979279620390802</v>
+        <v>0.2944636834107188</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2472243427880157</v>
+        <v>0.2491243427880157</v>
       </c>
       <c r="C88">
-        <v>-124.0787539130491</v>
+        <v>-127.058187547877</v>
       </c>
       <c r="D88">
-        <v>57.19124608695093</v>
+        <v>56.65681245212298</v>
       </c>
       <c r="E88">
-        <v>156.57</v>
+        <v>159.015</v>
       </c>
       <c r="F88">
-        <v>210.27</v>
+        <v>212.715</v>
       </c>
       <c r="G88">
         <v>29</v>
@@ -8634,37 +8634,37 @@
         <v>14.6</v>
       </c>
       <c r="M88">
-        <v>49.58166600000001</v>
+        <v>50.158197</v>
       </c>
       <c r="N88">
-        <v>-34.981666</v>
+        <v>-35.558197</v>
       </c>
       <c r="O88">
-        <v>-8.745416500000001</v>
+        <v>-8.88954925</v>
       </c>
       <c r="P88">
-        <v>-26.2362495</v>
+        <v>-26.66864775</v>
       </c>
       <c r="Q88">
-        <v>-9.336249500000005</v>
+        <v>-9.76864775</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4240340581849207</v>
+        <v>0.4531289857376069</v>
       </c>
       <c r="T88">
-        <v>7.372485800706388</v>
+        <v>7.939600093068417</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07361592085267969</v>
+        <v>0.07276976084287878</v>
       </c>
       <c r="W88">
-        <v>0.2184413658629381</v>
+        <v>0.2186408903932492</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2944636834107188</v>
+        <v>0.2910790433715151</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2491243427880157</v>
+        <v>0.2510243427880157</v>
       </c>
       <c r="C89">
-        <v>-127.058187547877</v>
+        <v>-130.0277254374695</v>
       </c>
       <c r="D89">
-        <v>56.65681245212298</v>
+        <v>56.13227456253048</v>
       </c>
       <c r="E89">
-        <v>159.015</v>
+        <v>161.46</v>
       </c>
       <c r="F89">
-        <v>212.715</v>
+        <v>215.16</v>
       </c>
       <c r="G89">
         <v>29</v>
@@ -8716,37 +8716,37 @@
         <v>14.6</v>
       </c>
       <c r="M89">
-        <v>50.158197</v>
+        <v>50.734728</v>
       </c>
       <c r="N89">
-        <v>-35.558197</v>
+        <v>-36.134728</v>
       </c>
       <c r="O89">
-        <v>-8.88954925</v>
+        <v>-9.033682000000001</v>
       </c>
       <c r="P89">
-        <v>-26.66864775</v>
+        <v>-27.101046</v>
       </c>
       <c r="Q89">
-        <v>-9.76864775</v>
+        <v>-10.20104600000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4531289857376069</v>
+        <v>0.4870730678824075</v>
       </c>
       <c r="T89">
-        <v>7.939600093068417</v>
+        <v>8.601233434157452</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07276976084287878</v>
+        <v>0.07194283174239152</v>
       </c>
       <c r="W89">
-        <v>0.2186408903932492</v>
+        <v>0.2188358802751441</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2910790433715151</v>
+        <v>0.2877713269695661</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2510243427880157</v>
+        <v>0.2529243427880157</v>
       </c>
       <c r="C90">
-        <v>-130.0277254374695</v>
+        <v>-132.9876399097774</v>
       </c>
       <c r="D90">
-        <v>56.13227456253048</v>
+        <v>55.6173600902226</v>
       </c>
       <c r="E90">
-        <v>161.46</v>
+        <v>163.905</v>
       </c>
       <c r="F90">
-        <v>215.16</v>
+        <v>217.605</v>
       </c>
       <c r="G90">
         <v>29</v>
@@ -8798,37 +8798,37 @@
         <v>14.6</v>
       </c>
       <c r="M90">
-        <v>50.734728</v>
+        <v>51.311259</v>
       </c>
       <c r="N90">
-        <v>-36.134728</v>
+        <v>-36.711259</v>
       </c>
       <c r="O90">
-        <v>-9.033682000000001</v>
+        <v>-9.17781475</v>
       </c>
       <c r="P90">
-        <v>-27.101046</v>
+        <v>-27.53344425</v>
       </c>
       <c r="Q90">
-        <v>-10.20104600000001</v>
+        <v>-10.63344425</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4870730678824075</v>
+        <v>0.5271888013262627</v>
       </c>
       <c r="T90">
-        <v>8.601233434157452</v>
+        <v>9.383163746353585</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07194283174239152</v>
+        <v>0.07113448531831972</v>
       </c>
       <c r="W90">
-        <v>0.2188358802751441</v>
+        <v>0.2190264883619402</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2877713269695661</v>
+        <v>0.2845379412732789</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2529243427880157</v>
+        <v>0.2548243427880157</v>
       </c>
       <c r="C91">
-        <v>-132.9876399097774</v>
+        <v>-135.9381933910703</v>
       </c>
       <c r="D91">
-        <v>55.6173600902226</v>
+        <v>55.11180660892976</v>
       </c>
       <c r="E91">
-        <v>163.905</v>
+        <v>166.35</v>
       </c>
       <c r="F91">
-        <v>217.605</v>
+        <v>220.05</v>
       </c>
       <c r="G91">
         <v>29</v>
@@ -8880,37 +8880,37 @@
         <v>14.6</v>
       </c>
       <c r="M91">
-        <v>51.311259</v>
+        <v>51.88779</v>
       </c>
       <c r="N91">
-        <v>-36.711259</v>
+        <v>-37.28779</v>
       </c>
       <c r="O91">
-        <v>-9.17781475</v>
+        <v>-9.3219475</v>
       </c>
       <c r="P91">
-        <v>-27.53344425</v>
+        <v>-27.9658425</v>
       </c>
       <c r="Q91">
-        <v>-10.63344425</v>
+        <v>-11.0658425</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5271888013262627</v>
+        <v>0.5753276814588891</v>
       </c>
       <c r="T91">
-        <v>9.383163746353585</v>
+        <v>10.32148012098895</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07113448531831972</v>
+        <v>0.07034410214811616</v>
       </c>
       <c r="W91">
-        <v>0.2190264883619402</v>
+        <v>0.2192128607134742</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2845379412732789</v>
+        <v>0.2813764085924646</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2548243427880157</v>
+        <v>0.2567243427880157</v>
       </c>
       <c r="C92">
-        <v>-135.9381933910703</v>
+        <v>-138.8796388519064</v>
       </c>
       <c r="D92">
-        <v>55.11180660892976</v>
+        <v>54.61536114809358</v>
       </c>
       <c r="E92">
-        <v>166.35</v>
+        <v>168.795</v>
       </c>
       <c r="F92">
-        <v>220.05</v>
+        <v>222.495</v>
       </c>
       <c r="G92">
         <v>29</v>
@@ -8962,37 +8962,37 @@
         <v>14.6</v>
       </c>
       <c r="M92">
-        <v>51.88779</v>
+        <v>52.46432100000001</v>
       </c>
       <c r="N92">
-        <v>-37.28779</v>
+        <v>-37.864321</v>
       </c>
       <c r="O92">
-        <v>-9.3219475</v>
+        <v>-9.466080250000001</v>
       </c>
       <c r="P92">
-        <v>-27.9658425</v>
+        <v>-28.39824075</v>
       </c>
       <c r="Q92">
-        <v>-11.0658425</v>
+        <v>-11.49824075</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5753276814588891</v>
+        <v>0.6341640905098769</v>
       </c>
       <c r="T92">
-        <v>10.32148012098895</v>
+        <v>11.46831124554327</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07034410214811616</v>
+        <v>0.06957109003659839</v>
       </c>
       <c r="W92">
-        <v>0.2192128607134742</v>
+        <v>0.2193951369693701</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2813764085924646</v>
+        <v>0.2782843601463936</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2567243427880157</v>
+        <v>0.2586243427880157</v>
       </c>
       <c r="C93">
-        <v>-138.8796388519064</v>
+        <v>-141.812220229215</v>
       </c>
       <c r="D93">
-        <v>54.61536114809358</v>
+        <v>54.127779770785</v>
       </c>
       <c r="E93">
-        <v>168.795</v>
+        <v>171.24</v>
       </c>
       <c r="F93">
-        <v>222.495</v>
+        <v>224.94</v>
       </c>
       <c r="G93">
         <v>29</v>
@@ -9044,37 +9044,37 @@
         <v>14.6</v>
       </c>
       <c r="M93">
-        <v>52.46432100000001</v>
+        <v>53.040852</v>
       </c>
       <c r="N93">
-        <v>-37.864321</v>
+        <v>-38.440852</v>
       </c>
       <c r="O93">
-        <v>-9.466080250000001</v>
+        <v>-9.610213</v>
       </c>
       <c r="P93">
-        <v>-28.39824075</v>
+        <v>-28.830639</v>
       </c>
       <c r="Q93">
-        <v>-11.49824075</v>
+        <v>-11.930639</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6341640905098769</v>
+        <v>0.7077096018236115</v>
       </c>
       <c r="T93">
-        <v>11.46831124554327</v>
+        <v>12.90185015123619</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06957109003659839</v>
+        <v>0.06881488253620059</v>
       </c>
       <c r="W93">
-        <v>0.2193951369693701</v>
+        <v>0.2195734506979639</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2782843601463936</v>
+        <v>0.2752595301448024</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2586243427880157</v>
+        <v>0.2605243427880157</v>
       </c>
       <c r="C94">
-        <v>-141.812220229215</v>
+        <v>-144.7361728259685</v>
       </c>
       <c r="D94">
-        <v>54.127779770785</v>
+        <v>53.64882717403156</v>
       </c>
       <c r="E94">
-        <v>171.24</v>
+        <v>173.685</v>
       </c>
       <c r="F94">
-        <v>224.94</v>
+        <v>227.385</v>
       </c>
       <c r="G94">
         <v>29</v>
@@ -9126,37 +9126,37 @@
         <v>14.6</v>
       </c>
       <c r="M94">
-        <v>53.040852</v>
+        <v>53.617383</v>
       </c>
       <c r="N94">
-        <v>-38.440852</v>
+        <v>-39.017383</v>
       </c>
       <c r="O94">
-        <v>-9.610213</v>
+        <v>-9.754345750000001</v>
       </c>
       <c r="P94">
-        <v>-28.830639</v>
+        <v>-29.26303725</v>
       </c>
       <c r="Q94">
-        <v>-11.930639</v>
+        <v>-12.36303725</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7077096018236115</v>
+        <v>0.8022681163698419</v>
       </c>
       <c r="T94">
-        <v>12.90185015123619</v>
+        <v>14.74497160141279</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06881488253620059</v>
+        <v>0.06807493756269306</v>
       </c>
       <c r="W94">
-        <v>0.2195734506979639</v>
+        <v>0.219747929722717</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2752595301448024</v>
+        <v>0.2722997502507722</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2605243427880157</v>
+        <v>0.2624243427880157</v>
       </c>
       <c r="C95">
-        <v>-144.7361728259685</v>
+        <v>-147.6517236898222</v>
       </c>
       <c r="D95">
-        <v>53.64882717403156</v>
+        <v>53.17827631017779</v>
       </c>
       <c r="E95">
-        <v>173.685</v>
+        <v>176.13</v>
       </c>
       <c r="F95">
-        <v>227.385</v>
+        <v>229.83</v>
       </c>
       <c r="G95">
         <v>29</v>
@@ -9208,37 +9208,37 @@
         <v>14.6</v>
       </c>
       <c r="M95">
-        <v>53.617383</v>
+        <v>54.19391400000001</v>
       </c>
       <c r="N95">
-        <v>-39.017383</v>
+        <v>-39.59391400000001</v>
       </c>
       <c r="O95">
-        <v>-9.754345750000001</v>
+        <v>-9.898478500000001</v>
       </c>
       <c r="P95">
-        <v>-29.26303725</v>
+        <v>-29.6954355</v>
       </c>
       <c r="Q95">
-        <v>-12.36303725</v>
+        <v>-12.7954355</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8022681163698419</v>
+        <v>0.9283461357648157</v>
       </c>
       <c r="T95">
-        <v>14.74497160141279</v>
+        <v>17.20246686831492</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06807493756269306</v>
+        <v>0.06735073609926015</v>
       </c>
       <c r="W95">
-        <v>0.219747929722717</v>
+        <v>0.2199186964277945</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2722997502507722</v>
+        <v>0.2694029443970406</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2624243427880157</v>
+        <v>0.2643243427880158</v>
       </c>
       <c r="C96">
-        <v>-147.6517236898222</v>
+        <v>-150.5590919720019</v>
       </c>
       <c r="D96">
-        <v>53.17827631017779</v>
+        <v>52.7159080279981</v>
       </c>
       <c r="E96">
-        <v>176.13</v>
+        <v>178.575</v>
       </c>
       <c r="F96">
-        <v>229.83</v>
+        <v>232.275</v>
       </c>
       <c r="G96">
         <v>29</v>
@@ -9290,37 +9290,37 @@
         <v>14.6</v>
       </c>
       <c r="M96">
-        <v>54.19391400000001</v>
+        <v>54.770445</v>
       </c>
       <c r="N96">
-        <v>-39.59391400000001</v>
+        <v>-40.170445</v>
       </c>
       <c r="O96">
-        <v>-9.898478500000001</v>
+        <v>-10.04261125</v>
       </c>
       <c r="P96">
-        <v>-29.6954355</v>
+        <v>-30.12783375</v>
       </c>
       <c r="Q96">
-        <v>-12.7954355</v>
+        <v>-13.22783375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9283461357648157</v>
+        <v>1.10485536291778</v>
       </c>
       <c r="T96">
-        <v>17.20246686831492</v>
+        <v>20.64296024197792</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06735073609926015</v>
+        <v>0.06664178098242583</v>
       </c>
       <c r="W96">
-        <v>0.2199186964277945</v>
+        <v>0.220085868044344</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2694029443970406</v>
+        <v>0.2665671239297034</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2643243427880158</v>
+        <v>0.2662243427880157</v>
       </c>
       <c r="C97">
-        <v>-150.5590919720019</v>
+        <v>-153.4584892676287</v>
       </c>
       <c r="D97">
-        <v>52.7159080279981</v>
+        <v>52.26151073237127</v>
       </c>
       <c r="E97">
-        <v>178.575</v>
+        <v>181.02</v>
       </c>
       <c r="F97">
-        <v>232.275</v>
+        <v>234.72</v>
       </c>
       <c r="G97">
         <v>29</v>
@@ -9372,37 +9372,37 @@
         <v>14.6</v>
       </c>
       <c r="M97">
-        <v>54.770445</v>
+        <v>55.34697600000001</v>
       </c>
       <c r="N97">
-        <v>-40.170445</v>
+        <v>-40.74697600000001</v>
       </c>
       <c r="O97">
-        <v>-10.04261125</v>
+        <v>-10.186744</v>
       </c>
       <c r="P97">
-        <v>-30.12783375</v>
+        <v>-30.56023200000001</v>
       </c>
       <c r="Q97">
-        <v>-13.22783375</v>
+        <v>-13.66023200000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.10485536291778</v>
+        <v>1.369619203647225</v>
       </c>
       <c r="T97">
-        <v>20.64296024197792</v>
+        <v>25.80370030247241</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06664178098242583</v>
+        <v>0.06594759576385889</v>
       </c>
       <c r="W97">
-        <v>0.220085868044344</v>
+        <v>0.2202495569188821</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2665671239297034</v>
+        <v>0.2637903830554356</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2662243427880157</v>
+        <v>0.2681243427880157</v>
       </c>
       <c r="C98">
-        <v>-153.4584892676287</v>
+        <v>-156.3501199385948</v>
       </c>
       <c r="D98">
-        <v>52.26151073237127</v>
+        <v>51.8148800614052</v>
       </c>
       <c r="E98">
-        <v>181.02</v>
+        <v>183.465</v>
       </c>
       <c r="F98">
-        <v>234.72</v>
+        <v>237.165</v>
       </c>
       <c r="G98">
         <v>29</v>
@@ -9454,37 +9454,37 @@
         <v>14.6</v>
       </c>
       <c r="M98">
-        <v>55.34697600000001</v>
+        <v>55.923507</v>
       </c>
       <c r="N98">
-        <v>-40.746976</v>
+        <v>-41.323507</v>
       </c>
       <c r="O98">
-        <v>-10.186744</v>
+        <v>-10.33087675</v>
       </c>
       <c r="P98">
-        <v>-30.560232</v>
+        <v>-30.99263025</v>
       </c>
       <c r="Q98">
-        <v>-13.660232</v>
+        <v>-14.09263025</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.369619203647221</v>
+        <v>1.810892271529629</v>
       </c>
       <c r="T98">
-        <v>25.80370030247234</v>
+        <v>34.40493373662979</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06594759576385889</v>
+        <v>0.065267723642582</v>
       </c>
       <c r="W98">
-        <v>0.2202495569188821</v>
+        <v>0.2204098707650792</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2637903830554356</v>
+        <v>0.2610708945703281</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2681243427880157</v>
+        <v>0.2700243427880157</v>
       </c>
       <c r="C99">
-        <v>-156.3501199385948</v>
+        <v>-159.2341814200226</v>
       </c>
       <c r="D99">
-        <v>51.8148800614052</v>
+        <v>51.37581857997742</v>
       </c>
       <c r="E99">
-        <v>183.465</v>
+        <v>185.91</v>
       </c>
       <c r="F99">
-        <v>237.165</v>
+        <v>239.61</v>
       </c>
       <c r="G99">
         <v>29</v>
@@ -9536,37 +9536,37 @@
         <v>14.6</v>
       </c>
       <c r="M99">
-        <v>55.923507</v>
+        <v>56.500038</v>
       </c>
       <c r="N99">
-        <v>-41.323507</v>
+        <v>-41.900038</v>
       </c>
       <c r="O99">
-        <v>-10.33087675</v>
+        <v>-10.4750095</v>
       </c>
       <c r="P99">
-        <v>-30.99263025</v>
+        <v>-31.4250285</v>
       </c>
       <c r="Q99">
-        <v>-14.09263025</v>
+        <v>-14.5250285</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.810892271529629</v>
+        <v>2.693438407294443</v>
       </c>
       <c r="T99">
-        <v>34.40493373662979</v>
+        <v>51.60740060494467</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.065267723642582</v>
+        <v>0.06460172646255566</v>
       </c>
       <c r="W99">
-        <v>0.2204098707650792</v>
+        <v>0.2205669129001294</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2610708945703281</v>
+        <v>0.2584069058502226</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2700243427880157</v>
+        <v>0.2719243427880157</v>
       </c>
       <c r="C100">
-        <v>-159.2341814200226</v>
+        <v>-162.1108645112741</v>
       </c>
       <c r="D100">
-        <v>51.37581857997742</v>
+        <v>50.94413548872588</v>
       </c>
       <c r="E100">
-        <v>185.91</v>
+        <v>188.355</v>
       </c>
       <c r="F100">
-        <v>239.61</v>
+        <v>242.055</v>
       </c>
       <c r="G100">
         <v>29</v>
@@ -9618,37 +9618,37 @@
         <v>14.6</v>
       </c>
       <c r="M100">
-        <v>56.500038</v>
+        <v>57.07656900000001</v>
       </c>
       <c r="N100">
-        <v>-41.900038</v>
+        <v>-42.476569</v>
       </c>
       <c r="O100">
-        <v>-10.4750095</v>
+        <v>-10.61914225</v>
       </c>
       <c r="P100">
-        <v>-31.4250285</v>
+        <v>-31.85742675</v>
       </c>
       <c r="Q100">
-        <v>-14.5250285</v>
+        <v>-14.95742675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.693438407294443</v>
+        <v>5.341076814588885</v>
       </c>
       <c r="T100">
-        <v>51.60740060494467</v>
+        <v>103.2148012098893</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06460172646255566</v>
+        <v>0.06394918377101469</v>
       </c>
       <c r="W100">
-        <v>0.2205669129001294</v>
+        <v>0.2207207824667947</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2584069058502226</v>
+        <v>0.2557967350840588</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2719243427880157</v>
-      </c>
-      <c r="C101">
-        <v>-162.1108645112741</v>
-      </c>
-      <c r="D101">
-        <v>50.94413548872588</v>
-      </c>
-      <c r="E101">
-        <v>188.355</v>
-      </c>
-      <c r="F101">
-        <v>242.055</v>
-      </c>
-      <c r="G101">
-        <v>29</v>
-      </c>
-      <c r="H101">
-        <v>190.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.5</v>
-      </c>
-      <c r="K101">
-        <v>16.9</v>
-      </c>
-      <c r="L101">
-        <v>14.6</v>
-      </c>
-      <c r="M101">
-        <v>57.07656900000001</v>
-      </c>
-      <c r="N101">
-        <v>-42.476569</v>
-      </c>
-      <c r="O101">
-        <v>-10.61914225</v>
-      </c>
-      <c r="P101">
-        <v>-31.85742675</v>
-      </c>
-      <c r="Q101">
-        <v>-14.95742675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.341076814588885</v>
-      </c>
-      <c r="T101">
-        <v>103.2148012098893</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06394918377101469</v>
-      </c>
-      <c r="W101">
-        <v>0.2207207824667947</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2557967350840588</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
